--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927666</v>
+        <v>119927276</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504727</v>
+        <v>504730</v>
       </c>
       <c r="R33" t="n">
-        <v>7134707</v>
+        <v>7134689</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4377,6 +4377,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,7 +4408,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119927276</v>
+        <v>119931675</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4443,10 +4448,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504730</v>
+        <v>504635</v>
       </c>
       <c r="R34" t="n">
-        <v>7134689</v>
+        <v>7134639</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4483,7 +4488,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt, även på tall.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,10 +4515,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119931675</v>
+        <v>119927812</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4526,21 +4531,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,13 +4555,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504635</v>
+        <v>504703</v>
       </c>
       <c r="R35" t="n">
-        <v>7134639</v>
+        <v>7134764</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4586,11 +4591,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119927812</v>
+        <v>119927666</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>78262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504703</v>
+        <v>504727</v>
       </c>
       <c r="R36" t="n">
-        <v>7134764</v>
+        <v>7134707</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119929031</v>
+        <v>119929965</v>
       </c>
       <c r="B43" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5343,25 +5343,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504655</v>
+        <v>504693</v>
       </c>
       <c r="R43" t="n">
         <v>7134811</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119929965</v>
+        <v>119929031</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5445,25 +5445,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504693</v>
+        <v>504655</v>
       </c>
       <c r="R44" t="n">
         <v>7134811</v>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119931003</v>
+        <v>119927769</v>
       </c>
       <c r="B45" t="n">
-        <v>78263</v>
+        <v>90488</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504719</v>
+        <v>504699</v>
       </c>
       <c r="R45" t="n">
-        <v>7134660</v>
+        <v>7134737</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119927769</v>
+        <v>119931003</v>
       </c>
       <c r="B46" t="n">
-        <v>90488</v>
+        <v>78263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504699</v>
+        <v>504719</v>
       </c>
       <c r="R46" t="n">
-        <v>7134737</v>
+        <v>7134660</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119932366</v>
+        <v>119930511</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6470,49 +6470,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504587</v>
+        <v>504746</v>
       </c>
       <c r="R54" t="n">
-        <v>7134632</v>
+        <v>7134757</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6542,11 +6534,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack0åh</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6573,10 +6560,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119930511</v>
+        <v>119926813</v>
       </c>
       <c r="B55" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6585,25 +6572,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6613,13 +6600,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504746</v>
+        <v>504786</v>
       </c>
       <c r="R55" t="n">
-        <v>7134757</v>
+        <v>7134692</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6643,12 +6630,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6675,10 +6667,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119926813</v>
+        <v>119926777</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>12337</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6687,25 +6679,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>101283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6715,13 +6707,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504786</v>
+        <v>504784</v>
       </c>
       <c r="R56" t="n">
-        <v>7134692</v>
+        <v>7134696</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6755,7 +6747,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Gamla kläckhål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6782,10 +6774,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119926777</v>
+        <v>119930827</v>
       </c>
       <c r="B57" t="n">
-        <v>12337</v>
+        <v>78262</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6794,25 +6786,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101283</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6822,10 +6814,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504784</v>
+        <v>504752</v>
       </c>
       <c r="R57" t="n">
-        <v>7134696</v>
+        <v>7134670</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6852,17 +6844,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gamla kläckhål</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6889,10 +6876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119930827</v>
+        <v>119929519</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6905,21 +6892,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6929,13 +6916,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504752</v>
+        <v>504635</v>
       </c>
       <c r="R58" t="n">
-        <v>7134670</v>
+        <v>7134835</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6965,6 +6952,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6991,7 +6983,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119929519</v>
+        <v>119930231</v>
       </c>
       <c r="B59" t="n">
         <v>78526</v>
@@ -7031,13 +7023,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504635</v>
+        <v>504728</v>
       </c>
       <c r="R59" t="n">
-        <v>7134835</v>
+        <v>7134788</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7098,10 +7090,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119930231</v>
+        <v>119929026</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7114,21 +7106,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7130,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504728</v>
+        <v>504650</v>
       </c>
       <c r="R60" t="n">
-        <v>7134788</v>
+        <v>7134810</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7174,11 +7166,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7205,10 +7192,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119929026</v>
+        <v>119931444</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7221,21 +7208,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7245,13 +7232,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504650</v>
+        <v>504676</v>
       </c>
       <c r="R61" t="n">
-        <v>7134810</v>
+        <v>7134658</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7281,6 +7268,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7307,10 +7299,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119931444</v>
+        <v>119927326</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7323,21 +7315,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7347,13 +7339,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504676</v>
+        <v>504726</v>
       </c>
       <c r="R62" t="n">
-        <v>7134658</v>
+        <v>7134683</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7383,11 +7375,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7414,10 +7401,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119927326</v>
+        <v>119930639</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7430,21 +7417,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7454,10 +7441,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504726</v>
+        <v>504746</v>
       </c>
       <c r="R63" t="n">
-        <v>7134683</v>
+        <v>7134714</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7490,6 +7477,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7516,7 +7508,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119930639</v>
+        <v>119927785</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7556,10 +7548,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504746</v>
+        <v>504704</v>
       </c>
       <c r="R64" t="n">
-        <v>7134714</v>
+        <v>7134755</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7592,11 +7584,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7623,10 +7610,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119927785</v>
+        <v>119932667</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7635,41 +7622,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504704</v>
+        <v>504661</v>
       </c>
       <c r="R65" t="n">
-        <v>7134755</v>
+        <v>7134863</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7725,10 +7721,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119932667</v>
+        <v>119927975</v>
       </c>
       <c r="B66" t="n">
-        <v>56522</v>
+        <v>90527</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7741,46 +7737,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504661</v>
+        <v>504681</v>
       </c>
       <c r="R66" t="n">
-        <v>7134863</v>
+        <v>7134773</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7943,10 +7930,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119927975</v>
+        <v>119927937</v>
       </c>
       <c r="B68" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7955,25 +7942,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7983,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504681</v>
+        <v>504692</v>
       </c>
       <c r="R68" t="n">
-        <v>7134773</v>
+        <v>7134770</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8019,6 +8006,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8045,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119927937</v>
+        <v>119931297</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8061,37 +8053,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504692</v>
+        <v>504699</v>
       </c>
       <c r="R69" t="n">
-        <v>7134770</v>
+        <v>7134659</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8121,11 +8118,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8152,10 +8144,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119931297</v>
+        <v>119931555</v>
       </c>
       <c r="B70" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8168,39 +8160,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504699</v>
+        <v>504644</v>
       </c>
       <c r="R70" t="n">
-        <v>7134659</v>
+        <v>7134658</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8233,6 +8220,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8259,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119931555</v>
+        <v>119927179</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8271,25 +8263,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8299,13 +8291,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504644</v>
+        <v>504745</v>
       </c>
       <c r="R71" t="n">
-        <v>7134658</v>
+        <v>7134686</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8335,11 +8327,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8366,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119927179</v>
+        <v>119929476</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8378,25 +8365,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8406,13 +8393,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504745</v>
+        <v>504634</v>
       </c>
       <c r="R72" t="n">
-        <v>7134686</v>
+        <v>7134847</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8468,7 +8455,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119929476</v>
+        <v>119929993</v>
       </c>
       <c r="B73" t="n">
         <v>78262</v>
@@ -8508,13 +8495,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504634</v>
+        <v>504701</v>
       </c>
       <c r="R73" t="n">
-        <v>7134847</v>
+        <v>7134814</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8570,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119929993</v>
+        <v>119928953</v>
       </c>
       <c r="B74" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8586,21 +8573,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8610,10 +8597,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504701</v>
+        <v>504662</v>
       </c>
       <c r="R74" t="n">
-        <v>7134814</v>
+        <v>7134813</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8646,6 +8633,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8672,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119928953</v>
+        <v>119930718</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8688,21 +8680,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8712,10 +8704,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504662</v>
+        <v>504758</v>
       </c>
       <c r="R75" t="n">
-        <v>7134813</v>
+        <v>7134653</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8748,11 +8740,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8779,10 +8766,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119930718</v>
+        <v>119928356</v>
       </c>
       <c r="B76" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8795,21 +8782,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8819,13 +8806,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504758</v>
+        <v>504674</v>
       </c>
       <c r="R76" t="n">
-        <v>7134653</v>
+        <v>7134819</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8855,6 +8842,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8881,7 +8873,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119928356</v>
+        <v>119966717</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8917,14 +8909,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>504674</v>
+        <v>504773</v>
       </c>
       <c r="R77" t="n">
-        <v>7134819</v>
+        <v>7134719</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8988,7 +8980,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966717</v>
+        <v>119966716</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -9028,10 +9020,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504773</v>
+        <v>504767</v>
       </c>
       <c r="R78" t="n">
-        <v>7134719</v>
+        <v>7134698</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9095,10 +9087,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119966716</v>
+        <v>120056742</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9107,41 +9099,44 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504767</v>
+        <v>504768</v>
       </c>
       <c r="R79" t="n">
-        <v>7134698</v>
+        <v>7134630</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9165,17 +9160,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9184,28 +9179,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120056742</v>
+        <v>120056747</v>
       </c>
       <c r="B80" t="n">
-        <v>79511</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9218,21 +9214,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9245,10 +9241,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>504768</v>
+        <v>504755</v>
       </c>
       <c r="R80" t="n">
-        <v>7134630</v>
+        <v>7134686</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9281,11 +9277,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9313,10 +9304,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056747</v>
+        <v>120056729</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9325,25 +9316,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9356,10 +9347,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504755</v>
+        <v>504742</v>
       </c>
       <c r="R81" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9392,6 +9383,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9419,10 +9415,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056729</v>
+        <v>120056736</v>
       </c>
       <c r="B82" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9431,25 +9427,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9462,7 +9458,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504742</v>
+        <v>504758</v>
       </c>
       <c r="R82" t="n">
         <v>7134636</v>
@@ -9498,11 +9494,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9530,10 +9521,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056736</v>
+        <v>120056722</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9542,25 +9533,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9573,10 +9564,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504758</v>
+        <v>504718</v>
       </c>
       <c r="R83" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9636,10 +9627,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120056722</v>
+        <v>120056731</v>
       </c>
       <c r="B84" t="n">
-        <v>87406</v>
+        <v>79636</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9648,25 +9639,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9679,10 +9670,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>504718</v>
+        <v>504742</v>
       </c>
       <c r="R84" t="n">
-        <v>7134606</v>
+        <v>7134636</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9715,6 +9706,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9742,10 +9738,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120056731</v>
+        <v>119932366</v>
       </c>
       <c r="B85" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9754,44 +9750,49 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>504742</v>
+        <v>504587</v>
       </c>
       <c r="R85" t="n">
-        <v>7134636</v>
+        <v>7134632</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9815,17 +9816,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På sälglåga.</t>
+          <t>Ringhack0åh</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9834,19 +9835,18 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -6152,10 +6152,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119929852</v>
+        <v>119929139</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>78262</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,21 +6168,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504662</v>
+        <v>504645</v>
       </c>
       <c r="R51" t="n">
-        <v>7134848</v>
+        <v>7134818</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119929139</v>
+        <v>119929852</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6372,21 +6372,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504645</v>
+        <v>504662</v>
       </c>
       <c r="R53" t="n">
-        <v>7134818</v>
+        <v>7134848</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119927975</v>
+        <v>119930581</v>
       </c>
       <c r="B66" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7733,25 +7733,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7761,13 +7761,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504681</v>
+        <v>504741</v>
       </c>
       <c r="R66" t="n">
-        <v>7134773</v>
+        <v>7134737</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7797,6 +7797,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7823,10 +7828,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119930581</v>
+        <v>119927975</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7835,25 +7840,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,13 +7868,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504741</v>
+        <v>504681</v>
       </c>
       <c r="R67" t="n">
-        <v>7134737</v>
+        <v>7134773</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7899,11 +7904,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119931555</v>
+        <v>119929476</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504644</v>
+        <v>504634</v>
       </c>
       <c r="R70" t="n">
-        <v>7134658</v>
+        <v>7134847</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8220,11 +8220,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8353,10 +8348,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119929476</v>
+        <v>119931555</v>
       </c>
       <c r="B72" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8369,21 +8364,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,13 +8388,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504634</v>
+        <v>504644</v>
       </c>
       <c r="R72" t="n">
-        <v>7134847</v>
+        <v>7134658</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8429,6 +8424,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927276</v>
+        <v>119931788</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,25 +4313,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504730</v>
+        <v>504645</v>
       </c>
       <c r="R33" t="n">
-        <v>7134689</v>
+        <v>7134625</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4377,11 +4377,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,7 +4403,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119931675</v>
+        <v>119926813</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504635</v>
+        <v>504786</v>
       </c>
       <c r="R34" t="n">
-        <v>7134639</v>
+        <v>7134692</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4478,12 +4473,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4515,10 +4510,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119927812</v>
+        <v>119928953</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4531,21 +4526,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4555,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504703</v>
+        <v>504662</v>
       </c>
       <c r="R35" t="n">
-        <v>7134764</v>
+        <v>7134813</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4591,6 +4586,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119927666</v>
+        <v>119930524</v>
       </c>
       <c r="B36" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504727</v>
+        <v>504748</v>
       </c>
       <c r="R36" t="n">
-        <v>7134707</v>
+        <v>7134754</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119927365</v>
+        <v>119930775</v>
       </c>
       <c r="B37" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504727</v>
+        <v>504774</v>
       </c>
       <c r="R37" t="n">
-        <v>7134690</v>
+        <v>7134657</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4795,6 +4795,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,10 +4826,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119930524</v>
+        <v>119927769</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>90488</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4837,21 +4842,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>3242</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4861,13 +4866,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504748</v>
+        <v>504699</v>
       </c>
       <c r="R38" t="n">
-        <v>7134754</v>
+        <v>7134737</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4923,10 +4928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927959</v>
+        <v>119927331</v>
       </c>
       <c r="B39" t="n">
-        <v>90573</v>
+        <v>79636</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4939,21 +4944,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4963,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504676</v>
+        <v>504726</v>
       </c>
       <c r="R39" t="n">
-        <v>7134783</v>
+        <v>7134684</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119931788</v>
+        <v>119929026</v>
       </c>
       <c r="B40" t="n">
-        <v>90712</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5037,25 +5042,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5065,10 +5070,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504645</v>
+        <v>504650</v>
       </c>
       <c r="R40" t="n">
-        <v>7134625</v>
+        <v>7134810</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,10 +5132,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119930947</v>
+        <v>119931600</v>
       </c>
       <c r="B41" t="n">
-        <v>79642</v>
+        <v>79643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5143,21 +5148,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,13 +5172,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504733</v>
+        <v>504646</v>
       </c>
       <c r="R41" t="n">
-        <v>7134672</v>
+        <v>7134666</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5229,10 +5234,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119927331</v>
+        <v>119929031</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>79567</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5245,21 +5250,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5269,10 +5274,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504726</v>
+        <v>504655</v>
       </c>
       <c r="R42" t="n">
-        <v>7134684</v>
+        <v>7134811</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5331,10 +5336,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119929965</v>
+        <v>119929852</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5347,21 +5352,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504693</v>
+        <v>504662</v>
       </c>
       <c r="R43" t="n">
-        <v>7134811</v>
+        <v>7134848</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5433,10 +5438,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119929031</v>
+        <v>119927666</v>
       </c>
       <c r="B44" t="n">
-        <v>79567</v>
+        <v>78262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5445,25 +5450,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5473,10 +5478,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504655</v>
+        <v>504727</v>
       </c>
       <c r="R44" t="n">
-        <v>7134811</v>
+        <v>7134707</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5535,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119927769</v>
+        <v>119927746</v>
       </c>
       <c r="B45" t="n">
-        <v>90488</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5551,21 +5556,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5575,13 +5580,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504699</v>
+        <v>504709</v>
       </c>
       <c r="R45" t="n">
-        <v>7134737</v>
+        <v>7134715</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5637,10 +5642,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119931003</v>
+        <v>119931261</v>
       </c>
       <c r="B46" t="n">
-        <v>78263</v>
+        <v>90807</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5649,25 +5654,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5677,10 +5682,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504719</v>
+        <v>504693</v>
       </c>
       <c r="R46" t="n">
-        <v>7134660</v>
+        <v>7134662</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5739,10 +5744,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119927746</v>
+        <v>119927179</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5751,25 +5756,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5779,13 +5784,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504709</v>
+        <v>504745</v>
       </c>
       <c r="R47" t="n">
-        <v>7134715</v>
+        <v>7134686</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5841,10 +5846,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119930775</v>
+        <v>119930827</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5857,21 +5862,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5881,10 +5886,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504774</v>
+        <v>504752</v>
       </c>
       <c r="R48" t="n">
-        <v>7134657</v>
+        <v>7134670</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5917,11 +5922,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5948,10 +5948,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119930503</v>
+        <v>119930511</v>
       </c>
       <c r="B49" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5960,25 +5960,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504740</v>
+        <v>504746</v>
       </c>
       <c r="R49" t="n">
-        <v>7134766</v>
+        <v>7134757</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119931600</v>
+        <v>119929965</v>
       </c>
       <c r="B50" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6062,25 +6062,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6090,13 +6090,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504646</v>
+        <v>504693</v>
       </c>
       <c r="R50" t="n">
-        <v>7134666</v>
+        <v>7134811</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6152,10 +6152,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119929139</v>
+        <v>119928356</v>
       </c>
       <c r="B51" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,21 +6168,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6192,13 +6192,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504645</v>
+        <v>504674</v>
       </c>
       <c r="R51" t="n">
-        <v>7134818</v>
+        <v>7134819</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6228,6 +6228,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119931261</v>
+        <v>119927975</v>
       </c>
       <c r="B52" t="n">
-        <v>90807</v>
+        <v>90527</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6266,25 +6271,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>65</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6294,13 +6299,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504693</v>
+        <v>504681</v>
       </c>
       <c r="R52" t="n">
-        <v>7134662</v>
+        <v>7134773</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6356,10 +6361,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119929852</v>
+        <v>119927365</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>92030</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6372,21 +6377,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6396,13 +6401,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504662</v>
+        <v>504727</v>
       </c>
       <c r="R53" t="n">
-        <v>7134848</v>
+        <v>7134690</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6458,10 +6463,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119930511</v>
+        <v>119929139</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>78262</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6470,25 +6475,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6498,10 +6503,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504746</v>
+        <v>504645</v>
       </c>
       <c r="R54" t="n">
-        <v>7134757</v>
+        <v>7134818</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6560,7 +6565,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119926813</v>
+        <v>119929519</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6600,10 +6605,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504786</v>
+        <v>504635</v>
       </c>
       <c r="R55" t="n">
-        <v>7134692</v>
+        <v>7134835</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6630,12 +6635,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6667,10 +6672,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119926777</v>
+        <v>119931297</v>
       </c>
       <c r="B56" t="n">
-        <v>12337</v>
+        <v>57463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6679,41 +6684,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101283</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504784</v>
+        <v>504699</v>
       </c>
       <c r="R56" t="n">
-        <v>7134696</v>
+        <v>7134659</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6737,17 +6747,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gamla kläckhål</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6774,10 +6779,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119930827</v>
+        <v>119927785</v>
       </c>
       <c r="B57" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6790,21 +6795,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6814,10 +6819,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504752</v>
+        <v>504704</v>
       </c>
       <c r="R57" t="n">
-        <v>7134670</v>
+        <v>7134755</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6876,7 +6881,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119929519</v>
+        <v>119931555</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -6916,10 +6921,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504635</v>
+        <v>504644</v>
       </c>
       <c r="R58" t="n">
-        <v>7134835</v>
+        <v>7134658</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6983,7 +6988,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119930231</v>
+        <v>119930581</v>
       </c>
       <c r="B59" t="n">
         <v>78526</v>
@@ -7023,13 +7028,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504728</v>
+        <v>504741</v>
       </c>
       <c r="R59" t="n">
-        <v>7134788</v>
+        <v>7134737</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7090,10 +7095,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119929026</v>
+        <v>119929476</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7106,21 +7111,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7130,13 +7135,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504650</v>
+        <v>504634</v>
       </c>
       <c r="R60" t="n">
-        <v>7134810</v>
+        <v>7134847</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7192,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119931444</v>
+        <v>119927812</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7208,21 +7213,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7232,13 +7237,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504676</v>
+        <v>504703</v>
       </c>
       <c r="R61" t="n">
-        <v>7134658</v>
+        <v>7134764</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7268,11 +7273,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927326</v>
+        <v>119927276</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504726</v>
+        <v>504730</v>
       </c>
       <c r="R62" t="n">
-        <v>7134683</v>
+        <v>7134689</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7375,6 +7375,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7401,7 +7406,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119930639</v>
+        <v>119931675</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -7441,13 +7446,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504746</v>
+        <v>504635</v>
       </c>
       <c r="R63" t="n">
-        <v>7134714</v>
+        <v>7134639</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7508,10 +7513,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119927785</v>
+        <v>119929993</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7524,21 +7529,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7548,10 +7553,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504704</v>
+        <v>504701</v>
       </c>
       <c r="R64" t="n">
-        <v>7134755</v>
+        <v>7134814</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7610,10 +7615,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119932667</v>
+        <v>119930639</v>
       </c>
       <c r="B65" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7622,50 +7627,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504661</v>
+        <v>504746</v>
       </c>
       <c r="R65" t="n">
-        <v>7134863</v>
+        <v>7134714</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7695,6 +7691,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7721,10 +7722,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119930581</v>
+        <v>119932667</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7733,41 +7734,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504741</v>
+        <v>504661</v>
       </c>
       <c r="R66" t="n">
-        <v>7134737</v>
+        <v>7134863</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7797,11 +7807,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7828,10 +7833,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119927975</v>
+        <v>119927326</v>
       </c>
       <c r="B67" t="n">
-        <v>90527</v>
+        <v>79608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7840,25 +7845,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7868,13 +7873,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504681</v>
+        <v>504726</v>
       </c>
       <c r="R67" t="n">
-        <v>7134773</v>
+        <v>7134683</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7930,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119927937</v>
+        <v>119930503</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7946,21 +7951,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504692</v>
+        <v>504740</v>
       </c>
       <c r="R68" t="n">
-        <v>7134770</v>
+        <v>7134766</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8006,11 +8011,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8037,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119931297</v>
+        <v>119930718</v>
       </c>
       <c r="B69" t="n">
-        <v>57463</v>
+        <v>91834</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8053,42 +8053,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504699</v>
+        <v>504758</v>
       </c>
       <c r="R69" t="n">
-        <v>7134659</v>
+        <v>7134653</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8144,10 +8139,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119929476</v>
+        <v>119930231</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,21 +8155,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8179,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504634</v>
+        <v>504728</v>
       </c>
       <c r="R70" t="n">
-        <v>7134847</v>
+        <v>7134788</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8220,6 +8215,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8246,10 +8246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119927179</v>
+        <v>119930947</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>79642</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504745</v>
+        <v>504733</v>
       </c>
       <c r="R71" t="n">
-        <v>7134686</v>
+        <v>7134672</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8348,7 +8348,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119931555</v>
+        <v>119927937</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504644</v>
+        <v>504692</v>
       </c>
       <c r="R72" t="n">
-        <v>7134658</v>
+        <v>7134770</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8455,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119929993</v>
+        <v>119931444</v>
       </c>
       <c r="B73" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8471,21 +8471,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504701</v>
+        <v>504676</v>
       </c>
       <c r="R73" t="n">
-        <v>7134814</v>
+        <v>7134658</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8531,6 +8531,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8557,10 +8562,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119928953</v>
+        <v>119927959</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>90573</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8569,25 +8574,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8597,10 +8602,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504662</v>
+        <v>504676</v>
       </c>
       <c r="R74" t="n">
-        <v>7134813</v>
+        <v>7134783</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8633,11 +8638,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8664,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119930718</v>
+        <v>119931003</v>
       </c>
       <c r="B75" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8680,21 +8680,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504758</v>
+        <v>504719</v>
       </c>
       <c r="R75" t="n">
-        <v>7134653</v>
+        <v>7134660</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119928356</v>
+        <v>119966716</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -8802,14 +8802,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504674</v>
+        <v>504767</v>
       </c>
       <c r="R76" t="n">
-        <v>7134819</v>
+        <v>7134698</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119966716</v>
+        <v>120056729</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8996,37 +8996,40 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504767</v>
+        <v>504742</v>
       </c>
       <c r="R78" t="n">
-        <v>7134698</v>
+        <v>7134636</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9050,17 +9053,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9069,28 +9072,29 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056742</v>
+        <v>120056736</v>
       </c>
       <c r="B79" t="n">
-        <v>79511</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9103,21 +9107,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9130,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504768</v>
+        <v>504758</v>
       </c>
       <c r="R79" t="n">
-        <v>7134630</v>
+        <v>7134636</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9166,11 +9170,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9198,10 +9197,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120056747</v>
+        <v>120056742</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>79511</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9214,21 +9213,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9241,10 +9240,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>504755</v>
+        <v>504768</v>
       </c>
       <c r="R80" t="n">
-        <v>7134686</v>
+        <v>7134630</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9277,6 +9276,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9304,10 +9308,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056729</v>
+        <v>120056722</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>87406</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9320,21 +9324,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>4412</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9347,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504742</v>
+        <v>504718</v>
       </c>
       <c r="R81" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9383,11 +9387,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9415,10 +9414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056736</v>
+        <v>120056731</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>79636</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9431,21 +9430,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9458,7 +9457,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504758</v>
+        <v>504742</v>
       </c>
       <c r="R82" t="n">
         <v>7134636</v>
@@ -9494,6 +9493,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9521,10 +9525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056722</v>
+        <v>120056747</v>
       </c>
       <c r="B83" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9533,25 +9537,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9564,10 +9568,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504718</v>
+        <v>504755</v>
       </c>
       <c r="R83" t="n">
-        <v>7134606</v>
+        <v>7134686</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9627,10 +9631,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120056731</v>
+        <v>119932366</v>
       </c>
       <c r="B84" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9639,44 +9643,49 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>504742</v>
+        <v>504587</v>
       </c>
       <c r="R84" t="n">
-        <v>7134636</v>
+        <v>7134632</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9700,17 +9709,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På sälglåga.</t>
+          <t>Ringhack0åh</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9719,137 +9728,21 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>119932366</v>
-      </c>
-      <c r="B85" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Sönner-Storåberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>504587</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7134632</v>
-      </c>
-      <c r="S85" t="n">
-        <v>25</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack0åh</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119931788</v>
+        <v>119926813</v>
       </c>
       <c r="B33" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,25 +4313,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504645</v>
+        <v>504786</v>
       </c>
       <c r="R33" t="n">
-        <v>7134625</v>
+        <v>7134692</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4371,12 +4371,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,7 +4408,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119926813</v>
+        <v>119928953</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4443,13 +4448,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504786</v>
+        <v>504662</v>
       </c>
       <c r="R34" t="n">
-        <v>7134692</v>
+        <v>7134813</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4473,12 +4478,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4510,10 +4515,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119928953</v>
+        <v>119931788</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4522,25 +4527,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,10 +4555,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504662</v>
+        <v>504645</v>
       </c>
       <c r="R35" t="n">
-        <v>7134813</v>
+        <v>7134625</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4586,11 +4591,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119930524</v>
+        <v>119927769</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>90488</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>3242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504748</v>
+        <v>504699</v>
       </c>
       <c r="R36" t="n">
-        <v>7134754</v>
+        <v>7134737</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119930775</v>
+        <v>119927331</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504774</v>
+        <v>504726</v>
       </c>
       <c r="R37" t="n">
-        <v>7134657</v>
+        <v>7134684</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4795,11 +4795,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4826,10 +4821,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119927769</v>
+        <v>119930775</v>
       </c>
       <c r="B38" t="n">
-        <v>90488</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4842,21 +4837,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4866,10 +4861,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504699</v>
+        <v>504774</v>
       </c>
       <c r="R38" t="n">
-        <v>7134737</v>
+        <v>7134657</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4902,6 +4897,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927331</v>
+        <v>119930524</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4940,25 +4940,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4968,13 +4968,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504748</v>
       </c>
       <c r="R39" t="n">
-        <v>7134684</v>
+        <v>7134754</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6152,10 +6152,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119928356</v>
+        <v>119927975</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6164,25 +6164,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6192,13 +6192,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504674</v>
+        <v>504681</v>
       </c>
       <c r="R51" t="n">
-        <v>7134819</v>
+        <v>7134773</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6228,11 +6228,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6259,10 +6254,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119927975</v>
+        <v>119928356</v>
       </c>
       <c r="B52" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6271,25 +6266,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6299,13 +6294,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504681</v>
+        <v>504674</v>
       </c>
       <c r="R52" t="n">
-        <v>7134773</v>
+        <v>7134819</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6335,6 +6330,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -8562,10 +8562,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119927959</v>
+        <v>119931003</v>
       </c>
       <c r="B74" t="n">
-        <v>90573</v>
+        <v>78263</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8574,25 +8574,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504676</v>
+        <v>504719</v>
       </c>
       <c r="R74" t="n">
-        <v>7134783</v>
+        <v>7134660</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8664,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119931003</v>
+        <v>119927959</v>
       </c>
       <c r="B75" t="n">
-        <v>78263</v>
+        <v>90573</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8676,25 +8676,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>1205</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504719</v>
+        <v>504676</v>
       </c>
       <c r="R75" t="n">
-        <v>7134660</v>
+        <v>7134783</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056731</v>
+        <v>120056747</v>
       </c>
       <c r="B82" t="n">
-        <v>79636</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9430,21 +9430,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504742</v>
+        <v>504755</v>
       </c>
       <c r="R82" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9493,11 +9493,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9525,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056747</v>
+        <v>120056731</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>79636</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9541,21 +9536,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9568,10 +9563,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504755</v>
+        <v>504742</v>
       </c>
       <c r="R83" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9604,6 +9599,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,7 +4301,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119926813</v>
+        <v>119930639</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504786</v>
+        <v>504746</v>
       </c>
       <c r="R33" t="n">
-        <v>7134692</v>
+        <v>7134714</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119931788</v>
+        <v>119927785</v>
       </c>
       <c r="B35" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4527,25 +4527,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504645</v>
+        <v>504704</v>
       </c>
       <c r="R35" t="n">
-        <v>7134625</v>
+        <v>7134755</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119927769</v>
+        <v>119931003</v>
       </c>
       <c r="B36" t="n">
-        <v>90488</v>
+        <v>78263</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504699</v>
+        <v>504719</v>
       </c>
       <c r="R36" t="n">
-        <v>7134737</v>
+        <v>7134660</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119927331</v>
+        <v>119929031</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>79567</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504726</v>
+        <v>504655</v>
       </c>
       <c r="R37" t="n">
-        <v>7134684</v>
+        <v>7134811</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4821,7 +4821,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119930775</v>
+        <v>119928356</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504774</v>
+        <v>504674</v>
       </c>
       <c r="R38" t="n">
-        <v>7134657</v>
+        <v>7134819</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119930524</v>
+        <v>119927331</v>
       </c>
       <c r="B39" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4940,25 +4940,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4968,13 +4968,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504748</v>
+        <v>504726</v>
       </c>
       <c r="R39" t="n">
-        <v>7134754</v>
+        <v>7134684</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119931600</v>
+        <v>119927812</v>
       </c>
       <c r="B41" t="n">
-        <v>79643</v>
+        <v>90562</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5144,25 +5144,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5172,13 +5172,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504646</v>
+        <v>504703</v>
       </c>
       <c r="R41" t="n">
-        <v>7134666</v>
+        <v>7134764</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119929031</v>
+        <v>119931297</v>
       </c>
       <c r="B42" t="n">
-        <v>79567</v>
+        <v>57463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5246,41 +5246,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504655</v>
+        <v>504699</v>
       </c>
       <c r="R42" t="n">
-        <v>7134811</v>
+        <v>7134659</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5336,10 +5341,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119929852</v>
+        <v>119927937</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5352,21 +5357,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5376,10 +5381,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504662</v>
+        <v>504692</v>
       </c>
       <c r="R43" t="n">
-        <v>7134848</v>
+        <v>7134770</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5412,6 +5417,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5438,10 +5448,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119927666</v>
+        <v>119931555</v>
       </c>
       <c r="B44" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5454,21 +5464,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5478,13 +5488,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504727</v>
+        <v>504644</v>
       </c>
       <c r="R44" t="n">
-        <v>7134707</v>
+        <v>7134658</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5514,6 +5524,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,10 +5555,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119927746</v>
+        <v>119929476</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5556,21 +5571,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5580,10 +5595,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504709</v>
+        <v>504634</v>
       </c>
       <c r="R45" t="n">
-        <v>7134715</v>
+        <v>7134847</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5642,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119931261</v>
+        <v>119930718</v>
       </c>
       <c r="B46" t="n">
-        <v>90807</v>
+        <v>91834</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5654,25 +5669,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5682,10 +5697,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504693</v>
+        <v>504758</v>
       </c>
       <c r="R46" t="n">
-        <v>7134662</v>
+        <v>7134653</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5744,10 +5759,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119927179</v>
+        <v>119931600</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>79643</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5760,21 +5775,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5784,13 +5799,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504745</v>
+        <v>504646</v>
       </c>
       <c r="R47" t="n">
-        <v>7134686</v>
+        <v>7134666</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5861,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119930827</v>
+        <v>119929139</v>
       </c>
       <c r="B48" t="n">
         <v>78262</v>
@@ -5886,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504752</v>
+        <v>504645</v>
       </c>
       <c r="R48" t="n">
-        <v>7134670</v>
+        <v>7134818</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5948,10 +5963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119930511</v>
+        <v>119927179</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5964,21 +5979,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5988,10 +6003,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504746</v>
+        <v>504745</v>
       </c>
       <c r="R49" t="n">
-        <v>7134757</v>
+        <v>7134686</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6050,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119929965</v>
+        <v>119927959</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>90573</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6062,25 +6077,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6090,10 +6105,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504693</v>
+        <v>504676</v>
       </c>
       <c r="R50" t="n">
-        <v>7134811</v>
+        <v>7134783</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6152,10 +6167,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119927975</v>
+        <v>119930947</v>
       </c>
       <c r="B51" t="n">
-        <v>90527</v>
+        <v>79642</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,21 +6183,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6192,13 +6207,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504681</v>
+        <v>504733</v>
       </c>
       <c r="R51" t="n">
-        <v>7134773</v>
+        <v>7134672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6254,7 +6269,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119928356</v>
+        <v>119930581</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6294,13 +6309,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504674</v>
+        <v>504741</v>
       </c>
       <c r="R52" t="n">
-        <v>7134819</v>
+        <v>7134737</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119927365</v>
+        <v>119927769</v>
       </c>
       <c r="B53" t="n">
-        <v>92030</v>
+        <v>90488</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6377,21 +6392,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6401,13 +6416,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504727</v>
+        <v>504699</v>
       </c>
       <c r="R53" t="n">
-        <v>7134690</v>
+        <v>7134737</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6463,10 +6478,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119929139</v>
+        <v>119930231</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6479,21 +6494,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6503,10 +6518,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504645</v>
+        <v>504728</v>
       </c>
       <c r="R54" t="n">
-        <v>7134818</v>
+        <v>7134788</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6539,6 +6554,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6565,10 +6585,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119929519</v>
+        <v>119927975</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6577,25 +6597,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6605,13 +6625,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504635</v>
+        <v>504681</v>
       </c>
       <c r="R55" t="n">
-        <v>7134835</v>
+        <v>7134773</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6641,11 +6661,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6672,10 +6687,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119931297</v>
+        <v>119927326</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>79608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6688,42 +6703,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504699</v>
+        <v>504726</v>
       </c>
       <c r="R56" t="n">
-        <v>7134659</v>
+        <v>7134683</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6779,7 +6789,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119927785</v>
+        <v>119929519</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6819,13 +6829,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504704</v>
+        <v>504635</v>
       </c>
       <c r="R57" t="n">
-        <v>7134755</v>
+        <v>7134835</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6855,6 +6865,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6881,10 +6896,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119931555</v>
+        <v>119927746</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6897,21 +6912,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6921,13 +6936,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504644</v>
+        <v>504709</v>
       </c>
       <c r="R58" t="n">
-        <v>7134658</v>
+        <v>7134715</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6957,11 +6972,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6988,10 +6998,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119930581</v>
+        <v>119932667</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7000,41 +7010,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504741</v>
+        <v>504661</v>
       </c>
       <c r="R59" t="n">
-        <v>7134737</v>
+        <v>7134863</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7064,11 +7083,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7095,10 +7109,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119929476</v>
+        <v>119930511</v>
       </c>
       <c r="B60" t="n">
-        <v>78262</v>
+        <v>79636</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7107,25 +7121,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7135,13 +7149,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504634</v>
+        <v>504746</v>
       </c>
       <c r="R60" t="n">
-        <v>7134847</v>
+        <v>7134757</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7197,10 +7211,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119927812</v>
+        <v>119927365</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>92030</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7213,21 +7227,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7237,13 +7251,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504703</v>
+        <v>504727</v>
       </c>
       <c r="R61" t="n">
-        <v>7134764</v>
+        <v>7134690</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7299,7 +7313,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927276</v>
+        <v>119929965</v>
       </c>
       <c r="B62" t="n">
         <v>78526</v>
@@ -7339,13 +7353,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504730</v>
+        <v>504693</v>
       </c>
       <c r="R62" t="n">
-        <v>7134689</v>
+        <v>7134811</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7375,11 +7389,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7406,7 +7415,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119931675</v>
+        <v>119927276</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -7446,10 +7455,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504635</v>
+        <v>504730</v>
       </c>
       <c r="R63" t="n">
-        <v>7134639</v>
+        <v>7134689</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7486,7 +7495,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7513,10 +7522,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119929993</v>
+        <v>119931444</v>
       </c>
       <c r="B64" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7529,21 +7538,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7553,13 +7562,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504701</v>
+        <v>504676</v>
       </c>
       <c r="R64" t="n">
-        <v>7134814</v>
+        <v>7134658</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7589,6 +7598,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7615,7 +7629,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119930639</v>
+        <v>119931675</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7655,13 +7669,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504746</v>
+        <v>504635</v>
       </c>
       <c r="R65" t="n">
-        <v>7134714</v>
+        <v>7134639</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7722,10 +7736,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119932667</v>
+        <v>119926813</v>
       </c>
       <c r="B66" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7734,47 +7748,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504661</v>
+        <v>504786</v>
       </c>
       <c r="R66" t="n">
-        <v>7134863</v>
+        <v>7134692</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7801,12 +7806,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7833,7 +7843,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119927326</v>
+        <v>119930524</v>
       </c>
       <c r="B67" t="n">
         <v>79608</v>
@@ -7873,13 +7883,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504726</v>
+        <v>504748</v>
       </c>
       <c r="R67" t="n">
-        <v>7134683</v>
+        <v>7134754</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7935,10 +7945,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119930503</v>
+        <v>119927666</v>
       </c>
       <c r="B68" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7951,21 +7961,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7975,10 +7985,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504740</v>
+        <v>504727</v>
       </c>
       <c r="R68" t="n">
-        <v>7134766</v>
+        <v>7134707</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8037,10 +8047,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119930718</v>
+        <v>119929993</v>
       </c>
       <c r="B69" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8053,21 +8063,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,10 +8087,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504758</v>
+        <v>504701</v>
       </c>
       <c r="R69" t="n">
-        <v>7134653</v>
+        <v>7134814</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8139,10 +8149,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119930231</v>
+        <v>119931788</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8151,25 +8161,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8179,10 +8189,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504728</v>
+        <v>504645</v>
       </c>
       <c r="R70" t="n">
-        <v>7134788</v>
+        <v>7134625</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8215,11 +8225,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8246,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119930947</v>
+        <v>119930503</v>
       </c>
       <c r="B71" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8258,25 +8263,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8286,10 +8291,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504733</v>
+        <v>504740</v>
       </c>
       <c r="R71" t="n">
-        <v>7134672</v>
+        <v>7134766</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8348,7 +8353,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119927937</v>
+        <v>119930775</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -8388,10 +8393,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504692</v>
+        <v>504774</v>
       </c>
       <c r="R72" t="n">
-        <v>7134770</v>
+        <v>7134657</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8455,10 +8460,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119931444</v>
+        <v>119930827</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8471,21 +8476,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,13 +8500,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504676</v>
+        <v>504752</v>
       </c>
       <c r="R73" t="n">
-        <v>7134658</v>
+        <v>7134670</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8531,11 +8536,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8562,10 +8562,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931003</v>
+        <v>119931261</v>
       </c>
       <c r="B74" t="n">
-        <v>78263</v>
+        <v>90807</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8574,25 +8574,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504719</v>
+        <v>504693</v>
       </c>
       <c r="R74" t="n">
-        <v>7134660</v>
+        <v>7134662</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8664,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119927959</v>
+        <v>119929852</v>
       </c>
       <c r="B75" t="n">
-        <v>90573</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8676,25 +8676,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504676</v>
+        <v>504662</v>
       </c>
       <c r="R75" t="n">
-        <v>7134783</v>
+        <v>7134848</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056729</v>
+        <v>120056722</v>
       </c>
       <c r="B78" t="n">
-        <v>79608</v>
+        <v>87406</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8996,21 +8996,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>4412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504742</v>
+        <v>504718</v>
       </c>
       <c r="R78" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9059,11 +9059,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9091,7 +9086,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056736</v>
+        <v>120056747</v>
       </c>
       <c r="B79" t="n">
         <v>91840</v>
@@ -9134,10 +9129,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504758</v>
+        <v>504755</v>
       </c>
       <c r="R79" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9308,10 +9303,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056722</v>
+        <v>120056731</v>
       </c>
       <c r="B81" t="n">
-        <v>87406</v>
+        <v>79636</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9320,25 +9315,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504718</v>
+        <v>504742</v>
       </c>
       <c r="R81" t="n">
-        <v>7134606</v>
+        <v>7134636</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9387,6 +9382,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9414,10 +9414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056747</v>
+        <v>120056729</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9426,25 +9426,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504755</v>
+        <v>504742</v>
       </c>
       <c r="R82" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9493,6 +9493,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9520,10 +9525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056731</v>
+        <v>120056736</v>
       </c>
       <c r="B83" t="n">
-        <v>79636</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9536,21 +9541,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9563,7 +9568,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504742</v>
+        <v>504758</v>
       </c>
       <c r="R83" t="n">
         <v>7134636</v>
@@ -9599,11 +9604,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -7843,10 +7843,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119930524</v>
+        <v>119927666</v>
       </c>
       <c r="B67" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7859,21 +7859,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7883,13 +7883,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504748</v>
+        <v>504727</v>
       </c>
       <c r="R67" t="n">
-        <v>7134754</v>
+        <v>7134707</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119927666</v>
+        <v>119929993</v>
       </c>
       <c r="B68" t="n">
         <v>78262</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504727</v>
+        <v>504701</v>
       </c>
       <c r="R68" t="n">
-        <v>7134707</v>
+        <v>7134814</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119929993</v>
+        <v>119930524</v>
       </c>
       <c r="B69" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8063,21 +8063,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8087,13 +8087,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504701</v>
+        <v>504748</v>
       </c>
       <c r="R69" t="n">
-        <v>7134814</v>
+        <v>7134754</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119930639</v>
+        <v>119927179</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,25 +4313,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504746</v>
+        <v>504745</v>
       </c>
       <c r="R33" t="n">
-        <v>7134714</v>
+        <v>7134686</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4377,11 +4377,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,7 +4403,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119928953</v>
+        <v>119931555</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4448,13 +4443,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504662</v>
+        <v>504644</v>
       </c>
       <c r="R34" t="n">
-        <v>7134813</v>
+        <v>7134658</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4515,7 +4510,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119927785</v>
+        <v>119928356</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4555,13 +4550,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504704</v>
+        <v>504674</v>
       </c>
       <c r="R35" t="n">
-        <v>7134755</v>
+        <v>7134819</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4591,6 +4586,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119931003</v>
+        <v>119930231</v>
       </c>
       <c r="B36" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504719</v>
+        <v>504728</v>
       </c>
       <c r="R36" t="n">
-        <v>7134660</v>
+        <v>7134788</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4693,6 +4693,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,10 +4724,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119929031</v>
+        <v>119930775</v>
       </c>
       <c r="B37" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4731,25 +4736,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4759,10 +4764,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504655</v>
+        <v>504774</v>
       </c>
       <c r="R37" t="n">
-        <v>7134811</v>
+        <v>7134657</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4795,6 +4800,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,10 +4831,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119928356</v>
+        <v>119929993</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4837,21 +4847,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4861,13 +4871,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504674</v>
+        <v>504701</v>
       </c>
       <c r="R38" t="n">
-        <v>7134819</v>
+        <v>7134814</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4897,11 +4907,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4928,10 +4933,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927331</v>
+        <v>119927975</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>90527</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4944,21 +4949,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4968,13 +4973,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504681</v>
       </c>
       <c r="R39" t="n">
-        <v>7134684</v>
+        <v>7134773</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5030,10 +5035,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119929026</v>
+        <v>119929965</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,21 +5051,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5070,10 +5075,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504650</v>
+        <v>504693</v>
       </c>
       <c r="R40" t="n">
-        <v>7134810</v>
+        <v>7134811</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119927812</v>
+        <v>119927769</v>
       </c>
       <c r="B41" t="n">
-        <v>90562</v>
+        <v>90488</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5148,21 +5153,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504703</v>
+        <v>504699</v>
       </c>
       <c r="R41" t="n">
-        <v>7134764</v>
+        <v>7134737</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5234,10 +5239,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119931297</v>
+        <v>119929852</v>
       </c>
       <c r="B42" t="n">
-        <v>57463</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5250,42 +5255,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504699</v>
+        <v>504662</v>
       </c>
       <c r="R42" t="n">
-        <v>7134659</v>
+        <v>7134848</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119927937</v>
+        <v>119930511</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,25 +5353,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504692</v>
+        <v>504746</v>
       </c>
       <c r="R43" t="n">
-        <v>7134770</v>
+        <v>7134757</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5417,11 +5417,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119931555</v>
+        <v>119929139</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5464,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5488,13 +5483,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504644</v>
+        <v>504645</v>
       </c>
       <c r="R44" t="n">
-        <v>7134658</v>
+        <v>7134818</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5524,11 +5519,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119929476</v>
+        <v>119929519</v>
       </c>
       <c r="B45" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5571,21 +5561,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,13 +5585,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504634</v>
+        <v>504635</v>
       </c>
       <c r="R45" t="n">
-        <v>7134847</v>
+        <v>7134835</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5631,6 +5621,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,10 +5652,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119930718</v>
+        <v>119931675</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5673,21 +5668,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5697,13 +5692,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504758</v>
+        <v>504635</v>
       </c>
       <c r="R46" t="n">
-        <v>7134653</v>
+        <v>7134639</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5733,6 +5728,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5759,10 +5759,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119931600</v>
+        <v>119930718</v>
       </c>
       <c r="B47" t="n">
-        <v>79643</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5771,25 +5771,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504646</v>
+        <v>504758</v>
       </c>
       <c r="R47" t="n">
-        <v>7134666</v>
+        <v>7134653</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119929139</v>
+        <v>119930947</v>
       </c>
       <c r="B48" t="n">
-        <v>78262</v>
+        <v>79642</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5873,25 +5873,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504645</v>
+        <v>504733</v>
       </c>
       <c r="R48" t="n">
-        <v>7134818</v>
+        <v>7134672</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119927179</v>
+        <v>119931261</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5975,25 +5975,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504745</v>
+        <v>504693</v>
       </c>
       <c r="R49" t="n">
-        <v>7134686</v>
+        <v>7134662</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119927959</v>
+        <v>119927785</v>
       </c>
       <c r="B50" t="n">
-        <v>90573</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6077,25 +6077,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504676</v>
+        <v>504704</v>
       </c>
       <c r="R50" t="n">
-        <v>7134783</v>
+        <v>7134755</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119930947</v>
+        <v>119931444</v>
       </c>
       <c r="B51" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6179,20 +6179,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504733</v>
+        <v>504676</v>
       </c>
       <c r="R51" t="n">
-        <v>7134672</v>
+        <v>7134658</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6243,6 +6243,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119930581</v>
+        <v>119927331</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6281,25 +6286,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6309,13 +6314,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504741</v>
+        <v>504726</v>
       </c>
       <c r="R52" t="n">
-        <v>7134737</v>
+        <v>7134684</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6345,11 +6350,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119927769</v>
+        <v>119926813</v>
       </c>
       <c r="B53" t="n">
-        <v>90488</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504699</v>
+        <v>504786</v>
       </c>
       <c r="R53" t="n">
-        <v>7134737</v>
+        <v>7134692</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,12 +6446,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6478,10 +6483,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119930231</v>
+        <v>119932667</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6490,41 +6495,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504728</v>
+        <v>504661</v>
       </c>
       <c r="R54" t="n">
-        <v>7134788</v>
+        <v>7134863</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6554,11 +6568,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6585,10 +6594,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119927975</v>
+        <v>119931003</v>
       </c>
       <c r="B55" t="n">
-        <v>90527</v>
+        <v>78263</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6597,25 +6606,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6625,13 +6634,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504681</v>
+        <v>504719</v>
       </c>
       <c r="R55" t="n">
-        <v>7134773</v>
+        <v>7134660</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6789,10 +6798,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119929519</v>
+        <v>119931297</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6805,34 +6814,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504635</v>
+        <v>504699</v>
       </c>
       <c r="R57" t="n">
-        <v>7134835</v>
+        <v>7134659</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6865,11 +6879,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6896,10 +6905,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119927746</v>
+        <v>119927959</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>90573</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6908,25 +6917,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6936,13 +6945,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504709</v>
+        <v>504676</v>
       </c>
       <c r="R58" t="n">
-        <v>7134715</v>
+        <v>7134783</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6998,10 +7007,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119932667</v>
+        <v>119927276</v>
       </c>
       <c r="B59" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7010,47 +7019,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504661</v>
+        <v>504730</v>
       </c>
       <c r="R59" t="n">
-        <v>7134863</v>
+        <v>7134689</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7083,6 +7083,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7109,10 +7114,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119930511</v>
+        <v>119930639</v>
       </c>
       <c r="B60" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7121,25 +7126,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7152,7 +7157,7 @@
         <v>504746</v>
       </c>
       <c r="R60" t="n">
-        <v>7134757</v>
+        <v>7134714</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7185,6 +7190,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7211,10 +7221,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119927365</v>
+        <v>119929031</v>
       </c>
       <c r="B61" t="n">
-        <v>92030</v>
+        <v>79567</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7223,25 +7233,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7251,13 +7261,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504727</v>
+        <v>504655</v>
       </c>
       <c r="R61" t="n">
-        <v>7134690</v>
+        <v>7134811</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7313,10 +7323,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119929965</v>
+        <v>119930827</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7329,21 +7339,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7353,10 +7363,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504693</v>
+        <v>504752</v>
       </c>
       <c r="R62" t="n">
-        <v>7134811</v>
+        <v>7134670</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7415,10 +7425,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119927276</v>
+        <v>119927812</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7431,21 +7441,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7455,13 +7465,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504730</v>
+        <v>504703</v>
       </c>
       <c r="R63" t="n">
-        <v>7134689</v>
+        <v>7134764</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7491,11 +7501,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7522,10 +7527,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119931444</v>
+        <v>119931788</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7534,25 +7539,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7562,13 +7567,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504676</v>
+        <v>504645</v>
       </c>
       <c r="R64" t="n">
-        <v>7134658</v>
+        <v>7134625</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7598,11 +7603,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7629,10 +7629,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119931675</v>
+        <v>119927365</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7669,13 +7669,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504635</v>
+        <v>504727</v>
       </c>
       <c r="R65" t="n">
-        <v>7134639</v>
+        <v>7134690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7705,11 +7705,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7736,10 +7731,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119926813</v>
+        <v>119929476</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7752,21 +7747,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7776,13 +7771,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504786</v>
+        <v>504634</v>
       </c>
       <c r="R66" t="n">
-        <v>7134692</v>
+        <v>7134847</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7806,17 +7801,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7843,10 +7833,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119927666</v>
+        <v>119930503</v>
       </c>
       <c r="B67" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7859,21 +7849,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7883,10 +7873,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504727</v>
+        <v>504740</v>
       </c>
       <c r="R67" t="n">
-        <v>7134707</v>
+        <v>7134766</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7945,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119929993</v>
+        <v>119929026</v>
       </c>
       <c r="B68" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7961,21 +7951,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7985,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504701</v>
+        <v>504650</v>
       </c>
       <c r="R68" t="n">
-        <v>7134814</v>
+        <v>7134810</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8047,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119930524</v>
+        <v>119928953</v>
       </c>
       <c r="B69" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8063,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8087,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504748</v>
+        <v>504662</v>
       </c>
       <c r="R69" t="n">
-        <v>7134754</v>
+        <v>7134813</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8123,6 +8113,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8149,10 +8144,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119931788</v>
+        <v>119927937</v>
       </c>
       <c r="B70" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8161,25 +8156,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8189,10 +8184,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504645</v>
+        <v>504692</v>
       </c>
       <c r="R70" t="n">
-        <v>7134625</v>
+        <v>7134770</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8225,6 +8220,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119930503</v>
+        <v>119927666</v>
       </c>
       <c r="B71" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8267,21 +8267,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504740</v>
+        <v>504727</v>
       </c>
       <c r="R71" t="n">
-        <v>7134766</v>
+        <v>7134707</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119930775</v>
+        <v>119930581</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -8393,13 +8393,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504774</v>
+        <v>504741</v>
       </c>
       <c r="R72" t="n">
-        <v>7134657</v>
+        <v>7134737</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119930827</v>
+        <v>119931600</v>
       </c>
       <c r="B73" t="n">
-        <v>78262</v>
+        <v>79643</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8472,25 +8472,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504752</v>
+        <v>504646</v>
       </c>
       <c r="R73" t="n">
-        <v>7134670</v>
+        <v>7134666</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8562,10 +8562,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931261</v>
+        <v>119927746</v>
       </c>
       <c r="B74" t="n">
-        <v>90807</v>
+        <v>78171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8574,25 +8574,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504693</v>
+        <v>504709</v>
       </c>
       <c r="R74" t="n">
-        <v>7134662</v>
+        <v>7134715</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119929852</v>
+        <v>119930524</v>
       </c>
       <c r="B75" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8680,21 +8680,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,13 +8704,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504662</v>
+        <v>504748</v>
       </c>
       <c r="R75" t="n">
-        <v>7134848</v>
+        <v>7134754</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966716</v>
+        <v>119966717</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504767</v>
+        <v>504773</v>
       </c>
       <c r="R76" t="n">
-        <v>7134698</v>
+        <v>7134719</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966717</v>
+        <v>119966716</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>504773</v>
+        <v>504767</v>
       </c>
       <c r="R77" t="n">
-        <v>7134719</v>
+        <v>7134698</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056722</v>
+        <v>120056747</v>
       </c>
       <c r="B78" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504718</v>
+        <v>504755</v>
       </c>
       <c r="R78" t="n">
-        <v>7134606</v>
+        <v>7134686</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056747</v>
+        <v>120056736</v>
       </c>
       <c r="B79" t="n">
         <v>91840</v>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504755</v>
+        <v>504758</v>
       </c>
       <c r="R79" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9303,10 +9303,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056731</v>
+        <v>120056729</v>
       </c>
       <c r="B81" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9315,25 +9315,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056729</v>
+        <v>120056731</v>
       </c>
       <c r="B82" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9426,25 +9426,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9525,10 +9525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056736</v>
+        <v>120056722</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9537,25 +9537,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504758</v>
+        <v>504718</v>
       </c>
       <c r="R83" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119927331</v>
+        <v>119932667</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>56522</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6290,37 +6290,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504726</v>
+        <v>504661</v>
       </c>
       <c r="R52" t="n">
-        <v>7134684</v>
+        <v>7134863</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6376,10 +6385,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119926813</v>
+        <v>119927331</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6388,25 +6397,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6416,13 +6425,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504786</v>
+        <v>504726</v>
       </c>
       <c r="R53" t="n">
-        <v>7134692</v>
+        <v>7134684</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,17 +6455,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6483,10 +6487,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119932667</v>
+        <v>119926813</v>
       </c>
       <c r="B54" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6495,47 +6499,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504661</v>
+        <v>504786</v>
       </c>
       <c r="R54" t="n">
-        <v>7134863</v>
+        <v>7134692</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6562,12 +6557,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7425,10 +7425,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119927812</v>
+        <v>119931788</v>
       </c>
       <c r="B63" t="n">
-        <v>90562</v>
+        <v>90712</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7437,25 +7437,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7465,10 +7465,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504703</v>
+        <v>504645</v>
       </c>
       <c r="R63" t="n">
-        <v>7134764</v>
+        <v>7134625</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7527,10 +7527,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119931788</v>
+        <v>119927812</v>
       </c>
       <c r="B64" t="n">
-        <v>90712</v>
+        <v>90562</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7539,25 +7539,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504645</v>
+        <v>504703</v>
       </c>
       <c r="R64" t="n">
-        <v>7134625</v>
+        <v>7134764</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119932667</v>
+        <v>119927331</v>
       </c>
       <c r="B52" t="n">
-        <v>56522</v>
+        <v>79636</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6290,46 +6290,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504661</v>
+        <v>504726</v>
       </c>
       <c r="R52" t="n">
-        <v>7134863</v>
+        <v>7134684</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6385,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119927331</v>
+        <v>119926813</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6397,25 +6388,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6425,13 +6416,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504726</v>
+        <v>504786</v>
       </c>
       <c r="R53" t="n">
-        <v>7134684</v>
+        <v>7134692</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6455,12 +6446,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6487,10 +6483,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119926813</v>
+        <v>119932667</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6499,38 +6495,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504786</v>
+        <v>504661</v>
       </c>
       <c r="R54" t="n">
-        <v>7134692</v>
+        <v>7134863</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6557,17 +6562,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927179</v>
+        <v>119927326</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>79624</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,25 +4313,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504745</v>
+        <v>504726</v>
       </c>
       <c r="R33" t="n">
-        <v>7134686</v>
+        <v>7134683</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4403,10 +4403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119931555</v>
+        <v>119929139</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504644</v>
+        <v>504645</v>
       </c>
       <c r="R34" t="n">
-        <v>7134658</v>
+        <v>7134818</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4479,11 +4479,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,10 +4505,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119928356</v>
+        <v>119927975</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4522,25 +4517,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,13 +4545,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504674</v>
+        <v>504681</v>
       </c>
       <c r="R35" t="n">
-        <v>7134819</v>
+        <v>7134773</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4586,11 +4581,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,10 +4607,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119930231</v>
+        <v>119930639</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4657,10 +4647,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504728</v>
+        <v>504746</v>
       </c>
       <c r="R36" t="n">
-        <v>7134788</v>
+        <v>7134714</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4724,10 +4714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119930775</v>
+        <v>119927959</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>90591</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4736,25 +4726,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4764,10 +4754,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504774</v>
+        <v>504676</v>
       </c>
       <c r="R37" t="n">
-        <v>7134657</v>
+        <v>7134783</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4800,11 +4790,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4831,10 +4816,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119929993</v>
+        <v>119930503</v>
       </c>
       <c r="B38" t="n">
-        <v>78262</v>
+        <v>79624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4847,21 +4832,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4871,10 +4856,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504701</v>
+        <v>504740</v>
       </c>
       <c r="R38" t="n">
-        <v>7134814</v>
+        <v>7134766</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4933,10 +4918,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927975</v>
+        <v>119927769</v>
       </c>
       <c r="B39" t="n">
-        <v>90527</v>
+        <v>90506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4945,25 +4930,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4973,13 +4958,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504681</v>
+        <v>504699</v>
       </c>
       <c r="R39" t="n">
-        <v>7134773</v>
+        <v>7134737</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5035,10 +5020,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119929965</v>
+        <v>119927276</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5075,13 +5060,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504693</v>
+        <v>504730</v>
       </c>
       <c r="R40" t="n">
-        <v>7134811</v>
+        <v>7134689</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5111,6 +5096,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5137,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119927769</v>
+        <v>119930511</v>
       </c>
       <c r="B41" t="n">
-        <v>90488</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5149,25 +5139,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5177,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504699</v>
+        <v>504746</v>
       </c>
       <c r="R41" t="n">
-        <v>7134737</v>
+        <v>7134757</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5239,10 +5229,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119929852</v>
+        <v>119932667</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>56532</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5251,41 +5241,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504662</v>
+        <v>504661</v>
       </c>
       <c r="R42" t="n">
-        <v>7134848</v>
+        <v>7134863</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5341,10 +5340,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119930511</v>
+        <v>119929965</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,25 +5352,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504746</v>
+        <v>504693</v>
       </c>
       <c r="R43" t="n">
-        <v>7134757</v>
+        <v>7134811</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5443,10 +5442,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119929139</v>
+        <v>119930775</v>
       </c>
       <c r="B44" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5459,21 +5458,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,10 +5482,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504645</v>
+        <v>504774</v>
       </c>
       <c r="R44" t="n">
-        <v>7134818</v>
+        <v>7134657</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5519,6 +5518,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5549,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119929519</v>
+        <v>119929993</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5561,21 +5565,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,13 +5589,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504635</v>
+        <v>504701</v>
       </c>
       <c r="R45" t="n">
-        <v>7134835</v>
+        <v>7134814</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5621,11 +5625,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5652,10 +5651,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119931675</v>
+        <v>119930947</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>79658</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5664,20 +5663,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5692,13 +5691,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504635</v>
+        <v>504733</v>
       </c>
       <c r="R46" t="n">
-        <v>7134639</v>
+        <v>7134672</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5728,11 +5727,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5759,10 +5753,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119930718</v>
+        <v>119927179</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5771,25 +5765,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5799,10 +5793,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504758</v>
+        <v>504745</v>
       </c>
       <c r="R47" t="n">
-        <v>7134653</v>
+        <v>7134686</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5861,10 +5855,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119930947</v>
+        <v>119930827</v>
       </c>
       <c r="B48" t="n">
-        <v>79642</v>
+        <v>78278</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5873,25 +5867,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5901,10 +5895,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504733</v>
+        <v>504752</v>
       </c>
       <c r="R48" t="n">
-        <v>7134672</v>
+        <v>7134670</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5963,10 +5957,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119931261</v>
+        <v>119928953</v>
       </c>
       <c r="B49" t="n">
-        <v>90807</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5975,25 +5969,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6003,10 +5997,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504693</v>
+        <v>504662</v>
       </c>
       <c r="R49" t="n">
-        <v>7134662</v>
+        <v>7134813</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6039,6 +6033,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6068,7 +6067,7 @@
         <v>119927785</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6167,10 +6166,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119931444</v>
+        <v>119927746</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6183,21 +6182,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6207,13 +6206,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504676</v>
+        <v>504709</v>
       </c>
       <c r="R51" t="n">
-        <v>7134658</v>
+        <v>7134715</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6243,11 +6242,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6274,10 +6268,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119927331</v>
+        <v>119927365</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>92048</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6286,25 +6280,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6314,13 +6308,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504726</v>
+        <v>504727</v>
       </c>
       <c r="R52" t="n">
-        <v>7134684</v>
+        <v>7134690</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6376,10 +6370,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119926813</v>
+        <v>119931297</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6392,34 +6386,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504786</v>
+        <v>504699</v>
       </c>
       <c r="R53" t="n">
-        <v>7134692</v>
+        <v>7134659</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6446,17 +6445,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6483,10 +6477,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119932667</v>
+        <v>119929852</v>
       </c>
       <c r="B54" t="n">
-        <v>56522</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6495,50 +6489,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504661</v>
+        <v>504662</v>
       </c>
       <c r="R54" t="n">
-        <v>7134863</v>
+        <v>7134848</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6594,10 +6579,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119931003</v>
+        <v>119927331</v>
       </c>
       <c r="B55" t="n">
-        <v>78263</v>
+        <v>79652</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6606,25 +6591,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6634,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504719</v>
+        <v>504726</v>
       </c>
       <c r="R55" t="n">
-        <v>7134660</v>
+        <v>7134684</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6696,10 +6681,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119927326</v>
+        <v>119930231</v>
       </c>
       <c r="B56" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6712,21 +6697,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6736,10 +6721,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504726</v>
+        <v>504728</v>
       </c>
       <c r="R56" t="n">
-        <v>7134683</v>
+        <v>7134788</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6772,6 +6757,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6798,10 +6788,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119931297</v>
+        <v>119930718</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>91852</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6814,42 +6804,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504699</v>
+        <v>504758</v>
       </c>
       <c r="R57" t="n">
-        <v>7134659</v>
+        <v>7134653</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6905,10 +6890,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119927959</v>
+        <v>119931003</v>
       </c>
       <c r="B58" t="n">
-        <v>90573</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6917,25 +6902,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6945,10 +6930,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504676</v>
+        <v>504719</v>
       </c>
       <c r="R58" t="n">
-        <v>7134783</v>
+        <v>7134660</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7007,10 +6992,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119927276</v>
+        <v>119931675</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7047,10 +7032,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504730</v>
+        <v>504635</v>
       </c>
       <c r="R59" t="n">
-        <v>7134689</v>
+        <v>7134639</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7087,7 +7072,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt, även på tall.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7114,10 +7099,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119930639</v>
+        <v>119926813</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7154,13 +7139,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504746</v>
+        <v>504786</v>
       </c>
       <c r="R60" t="n">
-        <v>7134714</v>
+        <v>7134692</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7184,12 +7169,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7224,7 +7209,7 @@
         <v>119929031</v>
       </c>
       <c r="B61" t="n">
-        <v>79567</v>
+        <v>79583</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7323,10 +7308,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119930827</v>
+        <v>119931600</v>
       </c>
       <c r="B62" t="n">
-        <v>78262</v>
+        <v>79659</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7335,25 +7320,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7363,13 +7348,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504752</v>
+        <v>504646</v>
       </c>
       <c r="R62" t="n">
-        <v>7134670</v>
+        <v>7134666</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7425,10 +7410,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119931788</v>
+        <v>119927937</v>
       </c>
       <c r="B63" t="n">
-        <v>90712</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7437,25 +7422,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7465,10 +7450,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504645</v>
+        <v>504692</v>
       </c>
       <c r="R63" t="n">
-        <v>7134625</v>
+        <v>7134770</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7501,6 +7486,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7527,10 +7517,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119927812</v>
+        <v>119929519</v>
       </c>
       <c r="B64" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7543,21 +7533,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7567,13 +7557,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504703</v>
+        <v>504635</v>
       </c>
       <c r="R64" t="n">
-        <v>7134764</v>
+        <v>7134835</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7603,6 +7593,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7629,10 +7624,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119927365</v>
+        <v>119930524</v>
       </c>
       <c r="B65" t="n">
-        <v>92030</v>
+        <v>79624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7645,21 +7640,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7669,10 +7664,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504727</v>
+        <v>504748</v>
       </c>
       <c r="R65" t="n">
-        <v>7134690</v>
+        <v>7134754</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7731,10 +7726,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119929476</v>
+        <v>119931555</v>
       </c>
       <c r="B66" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7747,21 +7742,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7771,13 +7766,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504634</v>
+        <v>504644</v>
       </c>
       <c r="R66" t="n">
-        <v>7134847</v>
+        <v>7134658</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7807,6 +7802,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7833,10 +7833,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119930503</v>
+        <v>119931261</v>
       </c>
       <c r="B67" t="n">
-        <v>79608</v>
+        <v>90825</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7845,25 +7845,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7873,10 +7873,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504740</v>
+        <v>504693</v>
       </c>
       <c r="R67" t="n">
-        <v>7134766</v>
+        <v>7134662</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7938,7 +7938,7 @@
         <v>119929026</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119928953</v>
+        <v>119928356</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504662</v>
+        <v>504674</v>
       </c>
       <c r="R69" t="n">
-        <v>7134813</v>
+        <v>7134819</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119927937</v>
+        <v>119929476</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504692</v>
+        <v>504634</v>
       </c>
       <c r="R70" t="n">
-        <v>7134770</v>
+        <v>7134847</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8220,11 +8220,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,10 +8246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119927666</v>
+        <v>119927812</v>
       </c>
       <c r="B71" t="n">
-        <v>78262</v>
+        <v>90580</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8267,21 +8262,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8291,10 +8286,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504727</v>
+        <v>504703</v>
       </c>
       <c r="R71" t="n">
-        <v>7134707</v>
+        <v>7134764</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8353,10 +8348,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119930581</v>
+        <v>119931788</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>90730</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8365,25 +8360,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,13 +8388,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504741</v>
+        <v>504645</v>
       </c>
       <c r="R72" t="n">
-        <v>7134737</v>
+        <v>7134625</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8429,11 +8424,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8460,10 +8450,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119931600</v>
+        <v>119927666</v>
       </c>
       <c r="B73" t="n">
-        <v>79643</v>
+        <v>78278</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8472,25 +8462,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8500,13 +8490,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504646</v>
+        <v>504727</v>
       </c>
       <c r="R73" t="n">
-        <v>7134666</v>
+        <v>7134707</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8562,10 +8552,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119927746</v>
+        <v>119930581</v>
       </c>
       <c r="B74" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8578,21 +8568,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8602,13 +8592,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504709</v>
+        <v>504741</v>
       </c>
       <c r="R74" t="n">
-        <v>7134715</v>
+        <v>7134737</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8638,6 +8628,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8664,10 +8659,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119930524</v>
+        <v>119931444</v>
       </c>
       <c r="B75" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8680,21 +8675,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,13 +8699,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504748</v>
+        <v>504676</v>
       </c>
       <c r="R75" t="n">
-        <v>7134754</v>
+        <v>7134658</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8740,6 +8735,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8769,7 +8769,7 @@
         <v>119966717</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>119966716</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>120056747</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9086,10 +9086,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056736</v>
+        <v>120056731</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>79652</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9102,21 +9102,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504758</v>
+        <v>504742</v>
       </c>
       <c r="R79" t="n">
         <v>7134636</v>
@@ -9165,6 +9165,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9192,10 +9197,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120056742</v>
+        <v>120056722</v>
       </c>
       <c r="B80" t="n">
-        <v>79511</v>
+        <v>87423</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9204,25 +9209,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>4412</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9240,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>504768</v>
+        <v>504718</v>
       </c>
       <c r="R80" t="n">
-        <v>7134630</v>
+        <v>7134606</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9271,11 +9276,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9303,10 +9303,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056729</v>
+        <v>120056736</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9315,25 +9315,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504742</v>
+        <v>504758</v>
       </c>
       <c r="R81" t="n">
         <v>7134636</v>
@@ -9382,11 +9382,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9414,10 +9409,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056731</v>
+        <v>120056742</v>
       </c>
       <c r="B82" t="n">
-        <v>79636</v>
+        <v>79527</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9430,21 +9425,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9457,10 +9452,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504742</v>
+        <v>504768</v>
       </c>
       <c r="R82" t="n">
-        <v>7134636</v>
+        <v>7134630</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9497,7 +9492,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På sälglåga.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9525,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056722</v>
+        <v>120056729</v>
       </c>
       <c r="B83" t="n">
-        <v>87406</v>
+        <v>79624</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9541,21 +9536,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4412</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9568,10 +9563,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504718</v>
+        <v>504742</v>
       </c>
       <c r="R83" t="n">
-        <v>7134606</v>
+        <v>7134636</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9604,6 +9599,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9634,7 +9634,7 @@
         <v>119932366</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4505,10 +4505,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119927975</v>
+        <v>119927959</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>90591</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4521,21 +4521,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504681</v>
+        <v>504676</v>
       </c>
       <c r="R35" t="n">
-        <v>7134773</v>
+        <v>7134783</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119930639</v>
+        <v>119927975</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4619,25 +4619,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504746</v>
+        <v>504681</v>
       </c>
       <c r="R36" t="n">
-        <v>7134714</v>
+        <v>7134773</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4683,11 +4683,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4714,10 +4709,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119927959</v>
+        <v>119930639</v>
       </c>
       <c r="B37" t="n">
-        <v>90591</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4726,25 +4721,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4754,10 +4749,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504676</v>
+        <v>504746</v>
       </c>
       <c r="R37" t="n">
-        <v>7134783</v>
+        <v>7134714</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4790,6 +4785,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4918,10 +4918,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927769</v>
+        <v>119927276</v>
       </c>
       <c r="B39" t="n">
-        <v>90506</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4934,21 +4934,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504699</v>
+        <v>504730</v>
       </c>
       <c r="R39" t="n">
-        <v>7134737</v>
+        <v>7134689</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4994,6 +4994,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5020,10 +5025,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119927276</v>
+        <v>119930511</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5032,25 +5037,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5060,13 +5065,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504730</v>
+        <v>504746</v>
       </c>
       <c r="R40" t="n">
-        <v>7134689</v>
+        <v>7134757</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5096,11 +5101,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5127,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119930511</v>
+        <v>119927769</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>90506</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,25 +5139,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504746</v>
+        <v>504699</v>
       </c>
       <c r="R41" t="n">
-        <v>7134757</v>
+        <v>7134737</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119927785</v>
+        <v>119927746</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,21 +6080,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6104,13 +6104,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504704</v>
+        <v>504709</v>
       </c>
       <c r="R50" t="n">
-        <v>7134755</v>
+        <v>7134715</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119927746</v>
+        <v>119927785</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6182,21 +6182,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,13 +6206,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504709</v>
+        <v>504704</v>
       </c>
       <c r="R51" t="n">
-        <v>7134715</v>
+        <v>7134755</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927326</v>
+        <v>119927937</v>
       </c>
       <c r="B33" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504726</v>
+        <v>504692</v>
       </c>
       <c r="R33" t="n">
-        <v>7134683</v>
+        <v>7134770</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4377,6 +4377,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,10 +4408,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119929139</v>
+        <v>119931788</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>90730</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4415,25 +4420,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4446,7 +4451,7 @@
         <v>504645</v>
       </c>
       <c r="R34" t="n">
-        <v>7134818</v>
+        <v>7134625</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4505,10 +4510,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119927959</v>
+        <v>119929852</v>
       </c>
       <c r="B35" t="n">
-        <v>90591</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4517,25 +4522,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4545,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504676</v>
+        <v>504662</v>
       </c>
       <c r="R35" t="n">
-        <v>7134783</v>
+        <v>7134848</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4607,10 +4612,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119927975</v>
+        <v>119927769</v>
       </c>
       <c r="B36" t="n">
-        <v>90545</v>
+        <v>90506</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4619,25 +4624,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4647,13 +4652,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504681</v>
+        <v>504699</v>
       </c>
       <c r="R36" t="n">
-        <v>7134773</v>
+        <v>7134737</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4709,7 +4714,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119930639</v>
+        <v>119930775</v>
       </c>
       <c r="B37" t="n">
         <v>78542</v>
@@ -4749,10 +4754,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504746</v>
+        <v>504774</v>
       </c>
       <c r="R37" t="n">
-        <v>7134714</v>
+        <v>7134657</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4816,10 +4821,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119930503</v>
+        <v>119927331</v>
       </c>
       <c r="B38" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4828,25 +4833,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4856,10 +4861,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504740</v>
+        <v>504726</v>
       </c>
       <c r="R38" t="n">
-        <v>7134766</v>
+        <v>7134684</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4918,10 +4923,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927276</v>
+        <v>119927326</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4934,21 +4939,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4958,13 +4963,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504730</v>
+        <v>504726</v>
       </c>
       <c r="R39" t="n">
-        <v>7134689</v>
+        <v>7134683</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4994,11 +4999,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5025,10 +5025,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119930511</v>
+        <v>119930827</v>
       </c>
       <c r="B40" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5037,25 +5037,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504746</v>
+        <v>504752</v>
       </c>
       <c r="R40" t="n">
-        <v>7134757</v>
+        <v>7134670</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119927769</v>
+        <v>119930511</v>
       </c>
       <c r="B41" t="n">
-        <v>90506</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,25 +5139,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504699</v>
+        <v>504746</v>
       </c>
       <c r="R41" t="n">
-        <v>7134737</v>
+        <v>7134757</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119932667</v>
+        <v>119927975</v>
       </c>
       <c r="B42" t="n">
-        <v>56532</v>
+        <v>90545</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5245,46 +5245,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504661</v>
+        <v>504681</v>
       </c>
       <c r="R42" t="n">
-        <v>7134863</v>
+        <v>7134773</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5331,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119929965</v>
+        <v>119929519</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -5380,13 +5371,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504693</v>
+        <v>504635</v>
       </c>
       <c r="R43" t="n">
-        <v>7134811</v>
+        <v>7134835</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5416,6 +5407,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,7 +5438,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119930775</v>
+        <v>119928953</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5482,10 +5478,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504774</v>
+        <v>504662</v>
       </c>
       <c r="R44" t="n">
-        <v>7134657</v>
+        <v>7134813</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5549,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119929993</v>
+        <v>119927746</v>
       </c>
       <c r="B45" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5565,21 +5561,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5589,13 +5585,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504701</v>
+        <v>504709</v>
       </c>
       <c r="R45" t="n">
-        <v>7134814</v>
+        <v>7134715</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5651,10 +5647,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119930947</v>
+        <v>119927276</v>
       </c>
       <c r="B46" t="n">
-        <v>79658</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5663,20 +5659,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5691,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504733</v>
+        <v>504730</v>
       </c>
       <c r="R46" t="n">
-        <v>7134672</v>
+        <v>7134689</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5727,6 +5723,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5753,10 +5754,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119927179</v>
+        <v>119929965</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5765,25 +5766,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5793,10 +5794,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504745</v>
+        <v>504693</v>
       </c>
       <c r="R47" t="n">
-        <v>7134686</v>
+        <v>7134811</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5855,7 +5856,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119930827</v>
+        <v>119929139</v>
       </c>
       <c r="B48" t="n">
         <v>78278</v>
@@ -5895,10 +5896,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504752</v>
+        <v>504645</v>
       </c>
       <c r="R48" t="n">
-        <v>7134670</v>
+        <v>7134818</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5957,10 +5958,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119928953</v>
+        <v>119929031</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5969,25 +5970,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5997,10 +5998,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504662</v>
+        <v>504655</v>
       </c>
       <c r="R49" t="n">
-        <v>7134813</v>
+        <v>7134811</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6033,11 +6034,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6064,10 +6060,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119927746</v>
+        <v>119930639</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,21 +6076,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6104,13 +6100,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504709</v>
+        <v>504746</v>
       </c>
       <c r="R50" t="n">
-        <v>7134715</v>
+        <v>7134714</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6140,6 +6136,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,10 +6167,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119927785</v>
+        <v>119929476</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6182,21 +6183,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,13 +6207,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504704</v>
+        <v>504634</v>
       </c>
       <c r="R51" t="n">
-        <v>7134755</v>
+        <v>7134847</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6268,10 +6269,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119927365</v>
+        <v>119931003</v>
       </c>
       <c r="B52" t="n">
-        <v>92048</v>
+        <v>78279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6284,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6308,13 +6309,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504727</v>
+        <v>504719</v>
       </c>
       <c r="R52" t="n">
-        <v>7134690</v>
+        <v>7134660</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6370,10 +6371,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119931297</v>
+        <v>119927179</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6382,46 +6383,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504699</v>
+        <v>504745</v>
       </c>
       <c r="R53" t="n">
-        <v>7134659</v>
+        <v>7134686</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6477,10 +6473,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119929852</v>
+        <v>119931297</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6493,37 +6489,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504662</v>
+        <v>504699</v>
       </c>
       <c r="R54" t="n">
-        <v>7134848</v>
+        <v>7134659</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6579,10 +6580,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119927331</v>
+        <v>119931261</v>
       </c>
       <c r="B55" t="n">
-        <v>79652</v>
+        <v>90825</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6591,25 +6592,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6619,10 +6620,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504726</v>
+        <v>504693</v>
       </c>
       <c r="R55" t="n">
-        <v>7134684</v>
+        <v>7134662</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6681,10 +6682,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119930231</v>
+        <v>119927666</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6697,21 +6698,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6721,10 +6722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504728</v>
+        <v>504727</v>
       </c>
       <c r="R56" t="n">
-        <v>7134788</v>
+        <v>7134707</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6757,11 +6758,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6788,10 +6784,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119930718</v>
+        <v>119932667</v>
       </c>
       <c r="B57" t="n">
-        <v>91852</v>
+        <v>56532</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6800,41 +6796,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504758</v>
+        <v>504661</v>
       </c>
       <c r="R57" t="n">
-        <v>7134653</v>
+        <v>7134863</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6890,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119931003</v>
+        <v>119928356</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6906,21 +6911,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6930,13 +6935,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504719</v>
+        <v>504674</v>
       </c>
       <c r="R58" t="n">
-        <v>7134660</v>
+        <v>7134819</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6966,6 +6971,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6992,7 +7002,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119931675</v>
+        <v>119926813</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -7032,10 +7042,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504635</v>
+        <v>504786</v>
       </c>
       <c r="R59" t="n">
-        <v>7134639</v>
+        <v>7134692</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7062,12 +7072,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7099,10 +7109,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119926813</v>
+        <v>119929993</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7115,21 +7125,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7139,13 +7149,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504786</v>
+        <v>504701</v>
       </c>
       <c r="R60" t="n">
-        <v>7134692</v>
+        <v>7134814</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7169,17 +7179,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7206,10 +7211,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119929031</v>
+        <v>119930947</v>
       </c>
       <c r="B61" t="n">
-        <v>79583</v>
+        <v>79658</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7222,21 +7227,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7246,10 +7251,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504655</v>
+        <v>504733</v>
       </c>
       <c r="R61" t="n">
-        <v>7134811</v>
+        <v>7134672</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7308,10 +7313,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119931600</v>
+        <v>119927959</v>
       </c>
       <c r="B62" t="n">
-        <v>79659</v>
+        <v>90591</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7324,21 +7329,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>1205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7348,13 +7353,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504646</v>
+        <v>504676</v>
       </c>
       <c r="R62" t="n">
-        <v>7134666</v>
+        <v>7134783</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7410,10 +7415,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119927937</v>
+        <v>119927365</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7426,21 +7431,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7450,13 +7455,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504692</v>
+        <v>504727</v>
       </c>
       <c r="R63" t="n">
-        <v>7134770</v>
+        <v>7134690</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7486,11 +7491,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7517,10 +7517,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119929519</v>
+        <v>119930524</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7533,21 +7533,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504635</v>
+        <v>504748</v>
       </c>
       <c r="R64" t="n">
-        <v>7134835</v>
+        <v>7134754</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7593,11 +7593,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7624,10 +7619,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119930524</v>
+        <v>119931675</v>
       </c>
       <c r="B65" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7640,21 +7635,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7664,13 +7659,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504748</v>
+        <v>504635</v>
       </c>
       <c r="R65" t="n">
-        <v>7134754</v>
+        <v>7134639</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7700,6 +7695,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7726,7 +7726,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119931555</v>
+        <v>119927785</v>
       </c>
       <c r="B66" t="n">
         <v>78542</v>
@@ -7766,13 +7766,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504644</v>
+        <v>504704</v>
       </c>
       <c r="R66" t="n">
-        <v>7134658</v>
+        <v>7134755</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7802,11 +7802,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7833,10 +7828,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119931261</v>
+        <v>119930581</v>
       </c>
       <c r="B67" t="n">
-        <v>90825</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7845,25 +7840,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7873,13 +7868,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504693</v>
+        <v>504741</v>
       </c>
       <c r="R67" t="n">
-        <v>7134662</v>
+        <v>7134737</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7909,6 +7904,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119929026</v>
+        <v>119927812</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7951,21 +7951,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504650</v>
+        <v>504703</v>
       </c>
       <c r="R68" t="n">
-        <v>7134810</v>
+        <v>7134764</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119928356</v>
+        <v>119930503</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8053,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504674</v>
+        <v>504740</v>
       </c>
       <c r="R69" t="n">
-        <v>7134819</v>
+        <v>7134766</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8113,11 +8113,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8144,10 +8139,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119929476</v>
+        <v>119930231</v>
       </c>
       <c r="B70" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,21 +8155,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8179,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504634</v>
+        <v>504728</v>
       </c>
       <c r="R70" t="n">
-        <v>7134847</v>
+        <v>7134788</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8220,6 +8215,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8246,10 +8246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119927812</v>
+        <v>119931555</v>
       </c>
       <c r="B71" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504703</v>
+        <v>504644</v>
       </c>
       <c r="R71" t="n">
-        <v>7134764</v>
+        <v>7134658</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8322,6 +8322,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8348,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119931788</v>
+        <v>119931444</v>
       </c>
       <c r="B72" t="n">
-        <v>90730</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8360,25 +8365,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8388,13 +8393,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504645</v>
+        <v>504676</v>
       </c>
       <c r="R72" t="n">
-        <v>7134625</v>
+        <v>7134658</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8424,6 +8429,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8450,10 +8460,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119927666</v>
+        <v>119930718</v>
       </c>
       <c r="B73" t="n">
-        <v>78278</v>
+        <v>91852</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8466,21 +8476,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504727</v>
+        <v>504758</v>
       </c>
       <c r="R73" t="n">
-        <v>7134707</v>
+        <v>7134653</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8552,10 +8562,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119930581</v>
+        <v>119931600</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8564,25 +8574,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8592,13 +8602,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504741</v>
+        <v>504646</v>
       </c>
       <c r="R74" t="n">
-        <v>7134737</v>
+        <v>7134666</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8628,11 +8638,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8659,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119931444</v>
+        <v>119929026</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8675,21 +8680,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8699,13 +8704,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504676</v>
+        <v>504650</v>
       </c>
       <c r="R75" t="n">
-        <v>7134658</v>
+        <v>7134810</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8735,11 +8740,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8766,7 +8766,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966717</v>
+        <v>119966716</v>
       </c>
       <c r="B76" t="n">
         <v>78542</v>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504773</v>
+        <v>504767</v>
       </c>
       <c r="R76" t="n">
-        <v>7134719</v>
+        <v>7134698</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966716</v>
+        <v>119966717</v>
       </c>
       <c r="B77" t="n">
         <v>78542</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>504767</v>
+        <v>504773</v>
       </c>
       <c r="R77" t="n">
-        <v>7134698</v>
+        <v>7134719</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056747</v>
+        <v>120056729</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504755</v>
+        <v>504742</v>
       </c>
       <c r="R78" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9059,6 +9059,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9086,10 +9091,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056731</v>
+        <v>120056747</v>
       </c>
       <c r="B79" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9102,21 +9107,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9129,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504742</v>
+        <v>504755</v>
       </c>
       <c r="R79" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9167,11 +9172,6 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9190,17 +9190,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120056722</v>
+        <v>120056742</v>
       </c>
       <c r="B80" t="n">
-        <v>87423</v>
+        <v>79527</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9209,25 +9209,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4412</v>
+        <v>6456</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>504718</v>
+        <v>504768</v>
       </c>
       <c r="R80" t="n">
-        <v>7134606</v>
+        <v>7134630</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9278,6 +9278,11 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9296,7 +9301,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9402,17 +9407,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056742</v>
+        <v>120056731</v>
       </c>
       <c r="B82" t="n">
-        <v>79527</v>
+        <v>79652</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9425,21 +9430,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9452,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504768</v>
+        <v>504742</v>
       </c>
       <c r="R82" t="n">
-        <v>7134630</v>
+        <v>7134636</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9492,7 +9497,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9520,10 +9525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056729</v>
+        <v>120056722</v>
       </c>
       <c r="B83" t="n">
-        <v>79624</v>
+        <v>87423</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9536,21 +9541,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>4412</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9563,10 +9568,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504742</v>
+        <v>504718</v>
       </c>
       <c r="R83" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9601,11 +9606,6 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -6371,10 +6371,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119927179</v>
+        <v>119931297</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6383,41 +6383,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504745</v>
+        <v>504699</v>
       </c>
       <c r="R53" t="n">
-        <v>7134686</v>
+        <v>7134659</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,10 +6478,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119931297</v>
+        <v>119927179</v>
       </c>
       <c r="B54" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6485,46 +6490,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504699</v>
+        <v>504745</v>
       </c>
       <c r="R54" t="n">
-        <v>7134659</v>
+        <v>7134686</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927959</v>
+        <v>119927365</v>
       </c>
       <c r="B62" t="n">
-        <v>90591</v>
+        <v>92048</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7325,25 +7325,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>2079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504676</v>
+        <v>504727</v>
       </c>
       <c r="R62" t="n">
-        <v>7134783</v>
+        <v>7134690</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119927365</v>
+        <v>119930524</v>
       </c>
       <c r="B63" t="n">
-        <v>92048</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7431,21 +7431,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504727</v>
+        <v>504748</v>
       </c>
       <c r="R63" t="n">
-        <v>7134690</v>
+        <v>7134754</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119930524</v>
+        <v>119927959</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>90591</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7529,25 +7529,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504748</v>
+        <v>504676</v>
       </c>
       <c r="R64" t="n">
-        <v>7134754</v>
+        <v>7134783</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,7 +4301,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927937</v>
+        <v>119927785</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504692</v>
+        <v>504704</v>
       </c>
       <c r="R33" t="n">
-        <v>7134770</v>
+        <v>7134755</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4377,11 +4377,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,10 +4403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119931788</v>
+        <v>119931555</v>
       </c>
       <c r="B34" t="n">
-        <v>90730</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4420,25 +4415,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4448,13 +4443,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504645</v>
+        <v>504644</v>
       </c>
       <c r="R34" t="n">
-        <v>7134625</v>
+        <v>7134658</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4484,6 +4479,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,10 +4510,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119929852</v>
+        <v>119929519</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,13 +4550,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504662</v>
+        <v>504635</v>
       </c>
       <c r="R35" t="n">
-        <v>7134848</v>
+        <v>7134835</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4586,6 +4586,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4612,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119927769</v>
+        <v>119929026</v>
       </c>
       <c r="B36" t="n">
-        <v>90506</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4628,21 +4633,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4652,10 +4657,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504699</v>
+        <v>504650</v>
       </c>
       <c r="R36" t="n">
-        <v>7134737</v>
+        <v>7134810</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4714,10 +4719,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119930775</v>
+        <v>119930827</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4730,21 +4735,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4754,10 +4759,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504774</v>
+        <v>504752</v>
       </c>
       <c r="R37" t="n">
-        <v>7134657</v>
+        <v>7134670</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4790,11 +4795,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,10 +4821,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119927331</v>
+        <v>119930718</v>
       </c>
       <c r="B38" t="n">
-        <v>79652</v>
+        <v>91852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4833,25 +4833,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504726</v>
+        <v>504758</v>
       </c>
       <c r="R38" t="n">
-        <v>7134684</v>
+        <v>7134653</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4923,10 +4923,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927326</v>
+        <v>119927179</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4935,25 +4935,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504745</v>
       </c>
       <c r="R39" t="n">
-        <v>7134683</v>
+        <v>7134686</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119930827</v>
+        <v>119929852</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5041,21 +5041,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504752</v>
+        <v>504662</v>
       </c>
       <c r="R40" t="n">
-        <v>7134670</v>
+        <v>7134848</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119930511</v>
+        <v>119929965</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,25 +5139,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504746</v>
+        <v>504693</v>
       </c>
       <c r="R41" t="n">
-        <v>7134757</v>
+        <v>7134811</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119927975</v>
+        <v>119931788</v>
       </c>
       <c r="B42" t="n">
-        <v>90545</v>
+        <v>90730</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5241,25 +5241,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5269,13 +5269,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504681</v>
+        <v>504645</v>
       </c>
       <c r="R42" t="n">
-        <v>7134773</v>
+        <v>7134625</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119929519</v>
+        <v>119930503</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,13 +5371,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504635</v>
+        <v>504740</v>
       </c>
       <c r="R43" t="n">
-        <v>7134835</v>
+        <v>7134766</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5407,11 +5407,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5438,10 +5433,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119928953</v>
+        <v>119927959</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>90591</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5450,25 +5445,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504662</v>
+        <v>504676</v>
       </c>
       <c r="R44" t="n">
-        <v>7134813</v>
+        <v>7134783</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5514,11 +5509,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,10 +5535,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119927746</v>
+        <v>119930511</v>
       </c>
       <c r="B45" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,25 +5547,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,13 +5575,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504709</v>
+        <v>504746</v>
       </c>
       <c r="R45" t="n">
-        <v>7134715</v>
+        <v>7134757</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5647,10 +5637,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119927276</v>
+        <v>119927769</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>90506</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5663,21 +5653,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5687,13 +5677,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504730</v>
+        <v>504699</v>
       </c>
       <c r="R46" t="n">
-        <v>7134689</v>
+        <v>7134737</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5723,11 +5713,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5754,10 +5739,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119929965</v>
+        <v>119930947</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5766,20 +5751,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5794,10 +5779,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504693</v>
+        <v>504733</v>
       </c>
       <c r="R47" t="n">
-        <v>7134811</v>
+        <v>7134672</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5856,10 +5841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119929139</v>
+        <v>119927365</v>
       </c>
       <c r="B48" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5872,21 +5857,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5896,13 +5881,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504645</v>
+        <v>504727</v>
       </c>
       <c r="R48" t="n">
-        <v>7134818</v>
+        <v>7134690</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6167,10 +6152,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119929476</v>
+        <v>119928356</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6183,21 +6168,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6207,13 +6192,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504634</v>
+        <v>504674</v>
       </c>
       <c r="R51" t="n">
-        <v>7134847</v>
+        <v>7134819</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6243,6 +6228,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119931003</v>
+        <v>119927326</v>
       </c>
       <c r="B52" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6285,21 +6275,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6309,10 +6299,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504719</v>
+        <v>504726</v>
       </c>
       <c r="R52" t="n">
-        <v>7134660</v>
+        <v>7134683</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6371,10 +6361,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119931297</v>
+        <v>119931444</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6387,39 +6377,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504699</v>
+        <v>504676</v>
       </c>
       <c r="R53" t="n">
-        <v>7134659</v>
+        <v>7134658</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6452,6 +6437,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6478,10 +6468,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119927179</v>
+        <v>119930524</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6490,25 +6480,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6518,13 +6508,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504745</v>
+        <v>504748</v>
       </c>
       <c r="R54" t="n">
-        <v>7134686</v>
+        <v>7134754</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6580,10 +6570,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119931261</v>
+        <v>119931600</v>
       </c>
       <c r="B55" t="n">
-        <v>90825</v>
+        <v>79659</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6592,25 +6582,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6620,13 +6610,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504693</v>
+        <v>504646</v>
       </c>
       <c r="R55" t="n">
-        <v>7134662</v>
+        <v>7134666</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6682,10 +6672,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119927666</v>
+        <v>119927276</v>
       </c>
       <c r="B56" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6698,21 +6688,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6722,13 +6712,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504727</v>
+        <v>504730</v>
       </c>
       <c r="R56" t="n">
-        <v>7134707</v>
+        <v>7134689</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6758,6 +6748,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6784,10 +6779,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119932667</v>
+        <v>119930775</v>
       </c>
       <c r="B57" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6796,50 +6791,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504661</v>
+        <v>504774</v>
       </c>
       <c r="R57" t="n">
-        <v>7134863</v>
+        <v>7134657</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6869,6 +6855,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6895,7 +6886,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119928356</v>
+        <v>119928953</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -6935,13 +6926,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504674</v>
+        <v>504662</v>
       </c>
       <c r="R58" t="n">
-        <v>7134819</v>
+        <v>7134813</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7002,10 +6993,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119926813</v>
+        <v>119927666</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7018,21 +7009,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7042,13 +7033,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504786</v>
+        <v>504727</v>
       </c>
       <c r="R59" t="n">
-        <v>7134692</v>
+        <v>7134707</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7072,17 +7063,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7109,7 +7095,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119929993</v>
+        <v>119929139</v>
       </c>
       <c r="B60" t="n">
         <v>78278</v>
@@ -7149,10 +7135,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504701</v>
+        <v>504645</v>
       </c>
       <c r="R60" t="n">
-        <v>7134814</v>
+        <v>7134818</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7211,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119930947</v>
+        <v>119927975</v>
       </c>
       <c r="B61" t="n">
-        <v>79658</v>
+        <v>90545</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7227,21 +7213,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7251,13 +7237,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504733</v>
+        <v>504681</v>
       </c>
       <c r="R61" t="n">
-        <v>7134672</v>
+        <v>7134773</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7313,10 +7299,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927365</v>
+        <v>119930231</v>
       </c>
       <c r="B62" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7329,21 +7315,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7353,13 +7339,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504727</v>
+        <v>504728</v>
       </c>
       <c r="R62" t="n">
-        <v>7134690</v>
+        <v>7134788</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7389,6 +7375,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7415,10 +7406,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119930524</v>
+        <v>119932667</v>
       </c>
       <c r="B63" t="n">
-        <v>79624</v>
+        <v>56532</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7427,41 +7418,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504748</v>
+        <v>504661</v>
       </c>
       <c r="R63" t="n">
-        <v>7134754</v>
+        <v>7134863</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119927959</v>
+        <v>119931003</v>
       </c>
       <c r="B64" t="n">
-        <v>90591</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7529,25 +7529,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7557,10 +7557,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504676</v>
+        <v>504719</v>
       </c>
       <c r="R64" t="n">
-        <v>7134783</v>
+        <v>7134660</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7726,7 +7726,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119927785</v>
+        <v>119927937</v>
       </c>
       <c r="B66" t="n">
         <v>78542</v>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504704</v>
+        <v>504692</v>
       </c>
       <c r="R66" t="n">
-        <v>7134755</v>
+        <v>7134770</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7802,6 +7802,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7828,7 +7833,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119930581</v>
+        <v>119926813</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -7868,13 +7873,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504741</v>
+        <v>504786</v>
       </c>
       <c r="R67" t="n">
-        <v>7134737</v>
+        <v>7134692</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,12 +7903,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8037,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119930503</v>
+        <v>119929476</v>
       </c>
       <c r="B69" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8053,21 +8058,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,13 +8082,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504740</v>
+        <v>504634</v>
       </c>
       <c r="R69" t="n">
-        <v>7134766</v>
+        <v>7134847</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8139,7 +8144,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119930231</v>
+        <v>119930581</v>
       </c>
       <c r="B70" t="n">
         <v>78542</v>
@@ -8179,13 +8184,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504728</v>
+        <v>504741</v>
       </c>
       <c r="R70" t="n">
-        <v>7134788</v>
+        <v>7134737</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8246,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119931555</v>
+        <v>119927331</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8258,25 +8263,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8286,13 +8291,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504644</v>
+        <v>504726</v>
       </c>
       <c r="R71" t="n">
-        <v>7134658</v>
+        <v>7134684</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8322,11 +8327,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8353,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119931444</v>
+        <v>119929993</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8369,21 +8369,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,13 +8393,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504676</v>
+        <v>504701</v>
       </c>
       <c r="R72" t="n">
-        <v>7134658</v>
+        <v>7134814</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8429,11 +8429,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8460,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119930718</v>
+        <v>119927746</v>
       </c>
       <c r="B73" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8476,21 +8471,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8500,13 +8495,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504758</v>
+        <v>504709</v>
       </c>
       <c r="R73" t="n">
-        <v>7134653</v>
+        <v>7134715</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8562,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931600</v>
+        <v>119931261</v>
       </c>
       <c r="B74" t="n">
-        <v>79659</v>
+        <v>90825</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8574,25 +8569,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>65</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8602,13 +8597,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504646</v>
+        <v>504693</v>
       </c>
       <c r="R74" t="n">
-        <v>7134666</v>
+        <v>7134662</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8664,10 +8659,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119929026</v>
+        <v>119931297</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8680,37 +8675,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504650</v>
+        <v>504699</v>
       </c>
       <c r="R75" t="n">
-        <v>7134810</v>
+        <v>7134659</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056729</v>
+        <v>120056731</v>
       </c>
       <c r="B78" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9091,10 +9091,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056747</v>
+        <v>120056729</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9103,25 +9103,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504755</v>
+        <v>504742</v>
       </c>
       <c r="R79" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9172,6 +9172,11 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9190,17 +9195,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120056742</v>
+        <v>120056736</v>
       </c>
       <c r="B80" t="n">
-        <v>79527</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9213,21 +9218,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9240,10 +9245,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>504768</v>
+        <v>504758</v>
       </c>
       <c r="R80" t="n">
-        <v>7134630</v>
+        <v>7134636</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9278,11 +9283,6 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9301,14 +9301,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056736</v>
+        <v>120056747</v>
       </c>
       <c r="B81" t="n">
         <v>91858</v>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504758</v>
+        <v>504755</v>
       </c>
       <c r="R81" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9407,17 +9407,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056731</v>
+        <v>120056722</v>
       </c>
       <c r="B82" t="n">
-        <v>79652</v>
+        <v>87423</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9426,25 +9426,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>4412</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504742</v>
+        <v>504718</v>
       </c>
       <c r="R82" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9493,11 +9493,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9525,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056722</v>
+        <v>120056742</v>
       </c>
       <c r="B83" t="n">
-        <v>87423</v>
+        <v>79527</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9537,25 +9532,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4412</v>
+        <v>6456</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9568,10 +9563,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504718</v>
+        <v>504768</v>
       </c>
       <c r="R83" t="n">
-        <v>7134606</v>
+        <v>7134630</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9606,6 +9601,11 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -6779,10 +6779,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119930775</v>
+        <v>119927666</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504774</v>
+        <v>504727</v>
       </c>
       <c r="R57" t="n">
-        <v>7134657</v>
+        <v>7134707</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6855,11 +6855,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6886,10 +6881,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119928953</v>
+        <v>119929139</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6902,21 +6897,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6926,10 +6921,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504662</v>
+        <v>504645</v>
       </c>
       <c r="R58" t="n">
-        <v>7134813</v>
+        <v>7134818</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6962,11 +6957,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6993,10 +6983,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119927666</v>
+        <v>119930775</v>
       </c>
       <c r="B59" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7009,21 +6999,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7033,10 +7023,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504727</v>
+        <v>504774</v>
       </c>
       <c r="R59" t="n">
-        <v>7134707</v>
+        <v>7134657</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7069,6 +7059,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7095,10 +7090,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119929139</v>
+        <v>119928953</v>
       </c>
       <c r="B60" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7111,21 +7106,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7135,10 +7130,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504645</v>
+        <v>504662</v>
       </c>
       <c r="R60" t="n">
-        <v>7134818</v>
+        <v>7134813</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7171,6 +7166,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7197,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119927975</v>
+        <v>119930231</v>
       </c>
       <c r="B61" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7209,25 +7209,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504681</v>
+        <v>504728</v>
       </c>
       <c r="R61" t="n">
-        <v>7134773</v>
+        <v>7134788</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7273,6 +7273,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7299,10 +7304,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119930231</v>
+        <v>119927975</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7311,25 +7316,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7339,13 +7344,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504728</v>
+        <v>504681</v>
       </c>
       <c r="R62" t="n">
-        <v>7134788</v>
+        <v>7134773</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7375,11 +7380,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7517,10 +7517,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119931003</v>
+        <v>119931675</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7533,21 +7533,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504719</v>
+        <v>504635</v>
       </c>
       <c r="R64" t="n">
-        <v>7134660</v>
+        <v>7134639</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7593,6 +7593,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7619,10 +7624,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119931675</v>
+        <v>119931003</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7635,21 +7640,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7659,13 +7664,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504635</v>
+        <v>504719</v>
       </c>
       <c r="R65" t="n">
-        <v>7134639</v>
+        <v>7134660</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7695,11 +7700,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8557,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931261</v>
+        <v>119931297</v>
       </c>
       <c r="B74" t="n">
-        <v>90825</v>
+        <v>57473</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8569,41 +8569,46 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504693</v>
+        <v>504699</v>
       </c>
       <c r="R74" t="n">
-        <v>7134662</v>
+        <v>7134659</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8659,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119931297</v>
+        <v>119931261</v>
       </c>
       <c r="B75" t="n">
-        <v>57473</v>
+        <v>90825</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8671,46 +8676,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504699</v>
+        <v>504693</v>
       </c>
       <c r="R75" t="n">
-        <v>7134659</v>
+        <v>7134662</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,7 +4301,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927785</v>
+        <v>119931555</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504704</v>
+        <v>504644</v>
       </c>
       <c r="R33" t="n">
-        <v>7134755</v>
+        <v>7134658</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4377,6 +4377,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,10 +4408,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119931555</v>
+        <v>119930947</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4415,20 +4420,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4443,13 +4448,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504644</v>
+        <v>504733</v>
       </c>
       <c r="R34" t="n">
-        <v>7134658</v>
+        <v>7134672</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4479,11 +4484,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,10 +4510,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119929519</v>
+        <v>119931600</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4522,25 +4522,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4550,13 +4550,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504635</v>
+        <v>504646</v>
       </c>
       <c r="R35" t="n">
-        <v>7134835</v>
+        <v>7134666</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4586,11 +4586,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,10 +4612,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119929026</v>
+        <v>119928356</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4633,21 +4628,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4657,13 +4652,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504650</v>
+        <v>504674</v>
       </c>
       <c r="R36" t="n">
-        <v>7134810</v>
+        <v>7134819</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4693,6 +4688,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119930827</v>
+        <v>119926813</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504752</v>
+        <v>504786</v>
       </c>
       <c r="R37" t="n">
-        <v>7134670</v>
+        <v>7134692</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4789,12 +4789,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,10 +4826,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119930718</v>
+        <v>119929476</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>78278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4837,21 +4842,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4861,13 +4866,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504758</v>
+        <v>504634</v>
       </c>
       <c r="R38" t="n">
-        <v>7134653</v>
+        <v>7134847</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4923,10 +4928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927179</v>
+        <v>119927785</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4935,25 +4940,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4963,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504745</v>
+        <v>504704</v>
       </c>
       <c r="R39" t="n">
-        <v>7134686</v>
+        <v>7134755</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119929852</v>
+        <v>119929139</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5041,21 +5046,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5065,10 +5070,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504662</v>
+        <v>504645</v>
       </c>
       <c r="R40" t="n">
-        <v>7134848</v>
+        <v>7134818</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,10 +5132,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119929965</v>
+        <v>119930511</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,25 +5144,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5172,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504693</v>
+        <v>504746</v>
       </c>
       <c r="R41" t="n">
-        <v>7134811</v>
+        <v>7134757</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5331,10 +5336,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119930503</v>
+        <v>119929031</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>79583</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5343,25 +5348,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504740</v>
+        <v>504655</v>
       </c>
       <c r="R43" t="n">
-        <v>7134766</v>
+        <v>7134811</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5433,10 +5438,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119927959</v>
+        <v>119929993</v>
       </c>
       <c r="B44" t="n">
-        <v>90591</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5445,25 +5450,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5473,10 +5478,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504676</v>
+        <v>504701</v>
       </c>
       <c r="R44" t="n">
-        <v>7134783</v>
+        <v>7134814</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5535,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119930511</v>
+        <v>119927975</v>
       </c>
       <c r="B45" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5551,21 +5556,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5575,13 +5580,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504746</v>
+        <v>504681</v>
       </c>
       <c r="R45" t="n">
-        <v>7134757</v>
+        <v>7134773</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5637,10 +5642,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119927769</v>
+        <v>119929852</v>
       </c>
       <c r="B46" t="n">
-        <v>90506</v>
+        <v>90598</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5653,21 +5658,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5677,10 +5682,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504699</v>
+        <v>504662</v>
       </c>
       <c r="R46" t="n">
-        <v>7134737</v>
+        <v>7134848</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5739,10 +5744,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119930947</v>
+        <v>119929026</v>
       </c>
       <c r="B47" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5751,25 +5756,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504733</v>
+        <v>504650</v>
       </c>
       <c r="R47" t="n">
-        <v>7134672</v>
+        <v>7134810</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5841,10 +5846,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119927365</v>
+        <v>119930775</v>
       </c>
       <c r="B48" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5857,21 +5862,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5881,13 +5886,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504727</v>
+        <v>504774</v>
       </c>
       <c r="R48" t="n">
-        <v>7134690</v>
+        <v>7134657</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5917,6 +5922,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5943,10 +5953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119929031</v>
+        <v>119928953</v>
       </c>
       <c r="B49" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5955,25 +5965,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5983,10 +5993,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504655</v>
+        <v>504662</v>
       </c>
       <c r="R49" t="n">
-        <v>7134811</v>
+        <v>7134813</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6019,6 +6029,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6045,10 +6060,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119930639</v>
+        <v>119932667</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6057,41 +6072,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504746</v>
+        <v>504661</v>
       </c>
       <c r="R50" t="n">
-        <v>7134714</v>
+        <v>7134863</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6121,11 +6145,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6152,10 +6171,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119928356</v>
+        <v>119927769</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>90506</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,21 +6187,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6192,13 +6211,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504674</v>
+        <v>504699</v>
       </c>
       <c r="R51" t="n">
-        <v>7134819</v>
+        <v>7134737</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6228,11 +6247,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6259,10 +6273,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119927326</v>
+        <v>119927179</v>
       </c>
       <c r="B52" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6271,25 +6285,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6299,10 +6313,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504726</v>
+        <v>504745</v>
       </c>
       <c r="R52" t="n">
-        <v>7134683</v>
+        <v>7134686</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6361,10 +6375,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119931444</v>
+        <v>119930827</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6377,21 +6391,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6401,13 +6415,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504676</v>
+        <v>504752</v>
       </c>
       <c r="R53" t="n">
-        <v>7134658</v>
+        <v>7134670</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6437,11 +6451,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6468,10 +6477,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119930524</v>
+        <v>119930581</v>
       </c>
       <c r="B54" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6484,21 +6493,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,13 +6517,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504748</v>
+        <v>504741</v>
       </c>
       <c r="R54" t="n">
-        <v>7134754</v>
+        <v>7134737</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6544,6 +6553,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6570,10 +6584,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119931600</v>
+        <v>119931675</v>
       </c>
       <c r="B55" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6582,25 +6596,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6610,13 +6624,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504646</v>
+        <v>504635</v>
       </c>
       <c r="R55" t="n">
-        <v>7134666</v>
+        <v>7134639</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6646,6 +6660,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6672,10 +6691,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119927276</v>
+        <v>119930524</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6688,21 +6707,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6712,13 +6731,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504730</v>
+        <v>504748</v>
       </c>
       <c r="R56" t="n">
-        <v>7134689</v>
+        <v>7134754</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6748,11 +6767,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6779,10 +6793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119927666</v>
+        <v>119929965</v>
       </c>
       <c r="B57" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6795,21 +6809,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6819,10 +6833,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504727</v>
+        <v>504693</v>
       </c>
       <c r="R57" t="n">
-        <v>7134707</v>
+        <v>7134811</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6881,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119929139</v>
+        <v>119927959</v>
       </c>
       <c r="B58" t="n">
-        <v>78278</v>
+        <v>90591</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6893,25 +6907,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6921,10 +6935,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504645</v>
+        <v>504676</v>
       </c>
       <c r="R58" t="n">
-        <v>7134818</v>
+        <v>7134783</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6983,7 +6997,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119930775</v>
+        <v>119927937</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -7023,10 +7037,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504774</v>
+        <v>504692</v>
       </c>
       <c r="R59" t="n">
-        <v>7134657</v>
+        <v>7134770</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7090,10 +7104,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119928953</v>
+        <v>119930718</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7106,21 +7120,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7130,10 +7144,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504662</v>
+        <v>504758</v>
       </c>
       <c r="R60" t="n">
-        <v>7134813</v>
+        <v>7134653</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7166,11 +7180,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7197,7 +7206,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119930231</v>
+        <v>119930639</v>
       </c>
       <c r="B61" t="n">
         <v>78542</v>
@@ -7237,10 +7246,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504728</v>
+        <v>504746</v>
       </c>
       <c r="R61" t="n">
-        <v>7134788</v>
+        <v>7134714</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7304,10 +7313,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927975</v>
+        <v>119927365</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>92048</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7316,25 +7325,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7344,10 +7353,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504681</v>
+        <v>504727</v>
       </c>
       <c r="R62" t="n">
-        <v>7134773</v>
+        <v>7134690</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7406,10 +7415,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119932667</v>
+        <v>119931444</v>
       </c>
       <c r="B63" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7418,47 +7427,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504661</v>
+        <v>504676</v>
       </c>
       <c r="R63" t="n">
-        <v>7134863</v>
+        <v>7134658</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7491,6 +7491,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7517,10 +7522,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119931675</v>
+        <v>119931261</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>90825</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7529,25 +7534,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7557,13 +7562,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504635</v>
+        <v>504693</v>
       </c>
       <c r="R64" t="n">
-        <v>7134639</v>
+        <v>7134662</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7593,11 +7598,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119931003</v>
+        <v>119927326</v>
       </c>
       <c r="B65" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504719</v>
+        <v>504726</v>
       </c>
       <c r="R65" t="n">
-        <v>7134660</v>
+        <v>7134683</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7726,10 +7726,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119927937</v>
+        <v>119927812</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504692</v>
+        <v>504703</v>
       </c>
       <c r="R66" t="n">
-        <v>7134770</v>
+        <v>7134764</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7802,11 +7802,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7833,10 +7828,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119926813</v>
+        <v>119930503</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7849,21 +7844,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7873,13 +7868,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504786</v>
+        <v>504740</v>
       </c>
       <c r="R67" t="n">
-        <v>7134692</v>
+        <v>7134766</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7903,17 +7898,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7940,10 +7930,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119927812</v>
+        <v>119927276</v>
       </c>
       <c r="B68" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7956,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7980,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504703</v>
+        <v>504730</v>
       </c>
       <c r="R68" t="n">
-        <v>7134764</v>
+        <v>7134689</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8016,6 +8006,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8042,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119929476</v>
+        <v>119927746</v>
       </c>
       <c r="B69" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8058,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8082,10 +8077,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504634</v>
+        <v>504709</v>
       </c>
       <c r="R69" t="n">
-        <v>7134847</v>
+        <v>7134715</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8144,10 +8139,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119930581</v>
+        <v>119927666</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,21 +8155,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8179,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504741</v>
+        <v>504727</v>
       </c>
       <c r="R70" t="n">
-        <v>7134737</v>
+        <v>7134707</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8220,11 +8215,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,10 +8241,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119927331</v>
+        <v>119931297</v>
       </c>
       <c r="B71" t="n">
-        <v>79652</v>
+        <v>57473</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8263,41 +8253,46 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504726</v>
+        <v>504699</v>
       </c>
       <c r="R71" t="n">
-        <v>7134684</v>
+        <v>7134659</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8353,10 +8348,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119929993</v>
+        <v>119929519</v>
       </c>
       <c r="B72" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8369,21 +8364,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,13 +8388,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504701</v>
+        <v>504635</v>
       </c>
       <c r="R72" t="n">
-        <v>7134814</v>
+        <v>7134835</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8429,6 +8424,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8455,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119927746</v>
+        <v>119927331</v>
       </c>
       <c r="B73" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8467,25 +8467,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504709</v>
+        <v>504726</v>
       </c>
       <c r="R73" t="n">
-        <v>7134715</v>
+        <v>7134684</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931297</v>
+        <v>119931003</v>
       </c>
       <c r="B74" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8573,42 +8573,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504699</v>
+        <v>504719</v>
       </c>
       <c r="R74" t="n">
-        <v>7134659</v>
+        <v>7134660</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8664,10 +8659,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119931261</v>
+        <v>119930231</v>
       </c>
       <c r="B75" t="n">
-        <v>90825</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8676,25 +8671,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,10 +8699,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504693</v>
+        <v>504728</v>
       </c>
       <c r="R75" t="n">
-        <v>7134662</v>
+        <v>7134788</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8740,6 +8735,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8766,7 +8766,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966716</v>
+        <v>119966717</v>
       </c>
       <c r="B76" t="n">
         <v>78542</v>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504767</v>
+        <v>504773</v>
       </c>
       <c r="R76" t="n">
-        <v>7134698</v>
+        <v>7134719</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966717</v>
+        <v>119966716</v>
       </c>
       <c r="B77" t="n">
         <v>78542</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>504773</v>
+        <v>504767</v>
       </c>
       <c r="R77" t="n">
-        <v>7134719</v>
+        <v>7134698</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056731</v>
+        <v>120056742</v>
       </c>
       <c r="B78" t="n">
-        <v>79652</v>
+        <v>79527</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8996,21 +8996,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504742</v>
+        <v>504768</v>
       </c>
       <c r="R78" t="n">
-        <v>7134636</v>
+        <v>7134630</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På sälglåga.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9091,10 +9091,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056729</v>
+        <v>120056747</v>
       </c>
       <c r="B79" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9103,25 +9103,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504742</v>
+        <v>504755</v>
       </c>
       <c r="R79" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9170,11 +9170,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9308,10 +9303,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056747</v>
+        <v>120056729</v>
       </c>
       <c r="B81" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9320,25 +9315,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504755</v>
+        <v>504742</v>
       </c>
       <c r="R81" t="n">
-        <v>7134686</v>
+        <v>7134636</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9387,6 +9382,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9520,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056742</v>
+        <v>120056731</v>
       </c>
       <c r="B83" t="n">
-        <v>79527</v>
+        <v>79652</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9536,21 +9536,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504768</v>
+        <v>504742</v>
       </c>
       <c r="R83" t="n">
-        <v>7134630</v>
+        <v>7134636</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119931555</v>
+        <v>119927812</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504644</v>
+        <v>504703</v>
       </c>
       <c r="R33" t="n">
-        <v>7134658</v>
+        <v>7134764</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4377,11 +4377,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,10 +4403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119930947</v>
+        <v>119929852</v>
       </c>
       <c r="B34" t="n">
-        <v>79658</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4420,25 +4415,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504733</v>
+        <v>504662</v>
       </c>
       <c r="R34" t="n">
-        <v>7134672</v>
+        <v>7134848</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4612,10 +4607,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119928356</v>
+        <v>119929139</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4628,21 +4623,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4652,13 +4647,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504674</v>
+        <v>504645</v>
       </c>
       <c r="R36" t="n">
-        <v>7134819</v>
+        <v>7134818</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4688,11 +4683,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,7 +4709,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119926813</v>
+        <v>119931675</v>
       </c>
       <c r="B37" t="n">
         <v>78542</v>
@@ -4759,10 +4749,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504786</v>
+        <v>504635</v>
       </c>
       <c r="R37" t="n">
-        <v>7134692</v>
+        <v>7134639</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4789,12 +4779,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4826,10 +4816,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119929476</v>
+        <v>119930231</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4842,21 +4832,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4866,13 +4856,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504634</v>
+        <v>504728</v>
       </c>
       <c r="R38" t="n">
-        <v>7134847</v>
+        <v>7134788</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4902,6 +4892,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4928,10 +4923,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927785</v>
+        <v>119927331</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4940,25 +4935,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4968,10 +4963,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504704</v>
+        <v>504726</v>
       </c>
       <c r="R39" t="n">
-        <v>7134755</v>
+        <v>7134684</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5030,10 +5025,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119929139</v>
+        <v>119930947</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5042,25 +5037,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5070,10 +5065,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504645</v>
+        <v>504733</v>
       </c>
       <c r="R40" t="n">
-        <v>7134818</v>
+        <v>7134672</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5132,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119930511</v>
+        <v>119927769</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>90506</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5144,25 +5139,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5172,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504746</v>
+        <v>504699</v>
       </c>
       <c r="R41" t="n">
-        <v>7134757</v>
+        <v>7134737</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5234,10 +5229,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119931788</v>
+        <v>119930775</v>
       </c>
       <c r="B42" t="n">
-        <v>90730</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5246,25 +5241,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5274,10 +5269,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504645</v>
+        <v>504774</v>
       </c>
       <c r="R42" t="n">
-        <v>7134625</v>
+        <v>7134657</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5310,6 +5305,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119929031</v>
+        <v>119927746</v>
       </c>
       <c r="B43" t="n">
-        <v>79583</v>
+        <v>78187</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5348,25 +5348,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5376,13 +5376,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504655</v>
+        <v>504709</v>
       </c>
       <c r="R43" t="n">
-        <v>7134811</v>
+        <v>7134715</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5438,10 +5438,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119929993</v>
+        <v>119931003</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504701</v>
+        <v>504719</v>
       </c>
       <c r="R44" t="n">
-        <v>7134814</v>
+        <v>7134660</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119927975</v>
+        <v>119927937</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5552,25 +5552,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504681</v>
+        <v>504692</v>
       </c>
       <c r="R45" t="n">
-        <v>7134773</v>
+        <v>7134770</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5616,6 +5616,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5642,10 +5647,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119929852</v>
+        <v>119927666</v>
       </c>
       <c r="B46" t="n">
-        <v>90598</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5658,21 +5663,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5682,10 +5687,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504662</v>
+        <v>504727</v>
       </c>
       <c r="R46" t="n">
-        <v>7134848</v>
+        <v>7134707</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5744,10 +5749,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119929026</v>
+        <v>119930639</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5760,21 +5765,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504650</v>
+        <v>504746</v>
       </c>
       <c r="R47" t="n">
-        <v>7134810</v>
+        <v>7134714</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5820,6 +5825,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5846,10 +5856,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119930775</v>
+        <v>119930511</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5858,25 +5868,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5886,10 +5896,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504774</v>
+        <v>504746</v>
       </c>
       <c r="R48" t="n">
-        <v>7134657</v>
+        <v>7134757</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5922,11 +5932,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,7 +5958,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119928953</v>
+        <v>119926813</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5993,13 +5998,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504662</v>
+        <v>504786</v>
       </c>
       <c r="R49" t="n">
-        <v>7134813</v>
+        <v>7134692</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6023,12 +6028,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6060,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119932667</v>
+        <v>119931297</v>
       </c>
       <c r="B50" t="n">
-        <v>56532</v>
+        <v>57473</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6072,35 +6077,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6109,10 +6110,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504661</v>
+        <v>504699</v>
       </c>
       <c r="R50" t="n">
-        <v>7134863</v>
+        <v>7134659</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6171,10 +6172,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119927769</v>
+        <v>119929965</v>
       </c>
       <c r="B51" t="n">
-        <v>90506</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6187,21 +6188,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6211,10 +6212,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504699</v>
+        <v>504693</v>
       </c>
       <c r="R51" t="n">
-        <v>7134737</v>
+        <v>7134811</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6273,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119927179</v>
+        <v>119931261</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6285,25 +6286,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6313,10 +6314,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504745</v>
+        <v>504693</v>
       </c>
       <c r="R52" t="n">
-        <v>7134686</v>
+        <v>7134662</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6375,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119930827</v>
+        <v>119927326</v>
       </c>
       <c r="B53" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6391,21 +6392,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6415,10 +6416,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504752</v>
+        <v>504726</v>
       </c>
       <c r="R53" t="n">
-        <v>7134670</v>
+        <v>7134683</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6477,10 +6478,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119930581</v>
+        <v>119930718</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6493,21 +6494,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6517,13 +6518,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504741</v>
+        <v>504758</v>
       </c>
       <c r="R54" t="n">
-        <v>7134737</v>
+        <v>7134653</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6553,11 +6554,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6584,10 +6580,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119931675</v>
+        <v>119931788</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90730</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6596,25 +6592,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6624,13 +6620,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504635</v>
+        <v>504645</v>
       </c>
       <c r="R55" t="n">
-        <v>7134639</v>
+        <v>7134625</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6660,11 +6656,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6793,7 +6784,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119929965</v>
+        <v>119927276</v>
       </c>
       <c r="B57" t="n">
         <v>78542</v>
@@ -6833,13 +6824,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504693</v>
+        <v>504730</v>
       </c>
       <c r="R57" t="n">
-        <v>7134811</v>
+        <v>7134689</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6869,6 +6860,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6895,10 +6891,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119927959</v>
+        <v>119931555</v>
       </c>
       <c r="B58" t="n">
-        <v>90591</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6907,25 +6903,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6935,13 +6931,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504676</v>
+        <v>504644</v>
       </c>
       <c r="R58" t="n">
-        <v>7134783</v>
+        <v>7134658</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6971,6 +6967,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6997,7 +6998,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119927937</v>
+        <v>119930581</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -7037,13 +7038,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504692</v>
+        <v>504741</v>
       </c>
       <c r="R59" t="n">
-        <v>7134770</v>
+        <v>7134737</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7104,10 +7105,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119930718</v>
+        <v>119927785</v>
       </c>
       <c r="B60" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7120,21 +7121,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7144,10 +7145,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504758</v>
+        <v>504704</v>
       </c>
       <c r="R60" t="n">
-        <v>7134653</v>
+        <v>7134755</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7206,10 +7207,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119930639</v>
+        <v>119932667</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7218,41 +7219,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504746</v>
+        <v>504661</v>
       </c>
       <c r="R61" t="n">
-        <v>7134714</v>
+        <v>7134863</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7282,11 +7292,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7522,10 +7527,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119931261</v>
+        <v>119929026</v>
       </c>
       <c r="B64" t="n">
-        <v>90825</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7534,25 +7539,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7562,10 +7567,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504693</v>
+        <v>504650</v>
       </c>
       <c r="R64" t="n">
-        <v>7134662</v>
+        <v>7134810</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7624,10 +7629,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119927326</v>
+        <v>119927179</v>
       </c>
       <c r="B65" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7636,25 +7641,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7664,10 +7669,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504726</v>
+        <v>504745</v>
       </c>
       <c r="R65" t="n">
-        <v>7134683</v>
+        <v>7134686</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7726,10 +7731,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119927812</v>
+        <v>119928356</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7742,21 +7747,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7766,13 +7771,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504703</v>
+        <v>504674</v>
       </c>
       <c r="R66" t="n">
-        <v>7134764</v>
+        <v>7134819</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7802,6 +7807,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7828,10 +7838,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119930503</v>
+        <v>119929993</v>
       </c>
       <c r="B67" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7844,21 +7854,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7868,10 +7878,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504740</v>
+        <v>504701</v>
       </c>
       <c r="R67" t="n">
-        <v>7134766</v>
+        <v>7134814</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7930,10 +7940,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119927276</v>
+        <v>119927975</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7942,25 +7952,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,13 +7980,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504730</v>
+        <v>504681</v>
       </c>
       <c r="R68" t="n">
-        <v>7134689</v>
+        <v>7134773</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8006,11 +8016,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8037,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119927746</v>
+        <v>119929476</v>
       </c>
       <c r="B69" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8053,21 +8058,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,10 +8082,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504709</v>
+        <v>504634</v>
       </c>
       <c r="R69" t="n">
-        <v>7134715</v>
+        <v>7134847</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8139,7 +8144,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119927666</v>
+        <v>119930827</v>
       </c>
       <c r="B70" t="n">
         <v>78278</v>
@@ -8179,10 +8184,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504727</v>
+        <v>504752</v>
       </c>
       <c r="R70" t="n">
-        <v>7134707</v>
+        <v>7134670</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8241,10 +8246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119931297</v>
+        <v>119927959</v>
       </c>
       <c r="B71" t="n">
-        <v>57473</v>
+        <v>90591</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8253,46 +8258,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504699</v>
+        <v>504676</v>
       </c>
       <c r="R71" t="n">
-        <v>7134659</v>
+        <v>7134783</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119929519</v>
+        <v>119930503</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8364,21 +8364,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504635</v>
+        <v>504740</v>
       </c>
       <c r="R72" t="n">
-        <v>7134835</v>
+        <v>7134766</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8424,11 +8424,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8455,10 +8450,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119927331</v>
+        <v>119929031</v>
       </c>
       <c r="B73" t="n">
-        <v>79652</v>
+        <v>79583</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8471,21 +8466,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,10 +8490,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504726</v>
+        <v>504655</v>
       </c>
       <c r="R73" t="n">
-        <v>7134684</v>
+        <v>7134811</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8557,10 +8552,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931003</v>
+        <v>119929519</v>
       </c>
       <c r="B74" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8573,21 +8568,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8597,13 +8592,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504719</v>
+        <v>504635</v>
       </c>
       <c r="R74" t="n">
-        <v>7134660</v>
+        <v>7134835</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8633,6 +8628,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8659,7 +8659,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119930231</v>
+        <v>119928953</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -8699,10 +8699,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504728</v>
+        <v>504662</v>
       </c>
       <c r="R75" t="n">
-        <v>7134788</v>
+        <v>7134813</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966717</v>
+        <v>119966716</v>
       </c>
       <c r="B76" t="n">
         <v>78542</v>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504773</v>
+        <v>504767</v>
       </c>
       <c r="R76" t="n">
-        <v>7134719</v>
+        <v>7134698</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966716</v>
+        <v>119966717</v>
       </c>
       <c r="B77" t="n">
         <v>78542</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>504767</v>
+        <v>504773</v>
       </c>
       <c r="R77" t="n">
-        <v>7134698</v>
+        <v>7134719</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056742</v>
+        <v>120056729</v>
       </c>
       <c r="B78" t="n">
-        <v>79527</v>
+        <v>79624</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504768</v>
+        <v>504742</v>
       </c>
       <c r="R78" t="n">
-        <v>7134630</v>
+        <v>7134636</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9091,10 +9091,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056747</v>
+        <v>120056722</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>87423</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9103,25 +9103,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504755</v>
+        <v>504718</v>
       </c>
       <c r="R79" t="n">
-        <v>7134686</v>
+        <v>7134606</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9303,10 +9303,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056729</v>
+        <v>120056747</v>
       </c>
       <c r="B81" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9315,25 +9315,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504742</v>
+        <v>504755</v>
       </c>
       <c r="R81" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9382,11 +9382,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9414,10 +9409,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056722</v>
+        <v>120056742</v>
       </c>
       <c r="B82" t="n">
-        <v>87423</v>
+        <v>79527</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9426,25 +9421,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4412</v>
+        <v>6456</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9457,10 +9452,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504718</v>
+        <v>504768</v>
       </c>
       <c r="R82" t="n">
-        <v>7134606</v>
+        <v>7134630</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9493,6 +9488,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119931261</v>
+        <v>119930718</v>
       </c>
       <c r="B52" t="n">
-        <v>90825</v>
+        <v>91852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6286,25 +6286,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504693</v>
+        <v>504758</v>
       </c>
       <c r="R52" t="n">
-        <v>7134662</v>
+        <v>7134653</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6376,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119927326</v>
+        <v>119931261</v>
       </c>
       <c r="B53" t="n">
-        <v>79624</v>
+        <v>90825</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6388,25 +6388,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504726</v>
+        <v>504693</v>
       </c>
       <c r="R53" t="n">
-        <v>7134683</v>
+        <v>7134662</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119930718</v>
+        <v>119927326</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>79624</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6494,21 +6494,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504758</v>
+        <v>504726</v>
       </c>
       <c r="R54" t="n">
-        <v>7134653</v>
+        <v>7134683</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119927975</v>
+        <v>119929476</v>
       </c>
       <c r="B68" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7952,25 +7952,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504681</v>
+        <v>504634</v>
       </c>
       <c r="R68" t="n">
-        <v>7134773</v>
+        <v>7134847</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119929476</v>
+        <v>119927975</v>
       </c>
       <c r="B69" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8054,25 +8054,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504634</v>
+        <v>504681</v>
       </c>
       <c r="R69" t="n">
-        <v>7134847</v>
+        <v>7134773</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8450,10 +8450,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119929031</v>
+        <v>119929519</v>
       </c>
       <c r="B73" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8462,25 +8462,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8490,13 +8490,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504655</v>
+        <v>504635</v>
       </c>
       <c r="R73" t="n">
-        <v>7134811</v>
+        <v>7134835</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8526,6 +8526,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8552,7 +8557,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119929519</v>
+        <v>119928953</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8592,13 +8597,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504635</v>
+        <v>504662</v>
       </c>
       <c r="R74" t="n">
-        <v>7134835</v>
+        <v>7134813</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8659,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119928953</v>
+        <v>119929031</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8671,25 +8676,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8699,10 +8704,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504662</v>
+        <v>504655</v>
       </c>
       <c r="R75" t="n">
-        <v>7134813</v>
+        <v>7134811</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8735,11 +8740,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4403,10 +4403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119929852</v>
+        <v>119930827</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504662</v>
+        <v>504752</v>
       </c>
       <c r="R34" t="n">
-        <v>7134848</v>
+        <v>7134670</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4505,10 +4505,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119931600</v>
+        <v>119927937</v>
       </c>
       <c r="B35" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4517,25 +4517,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504646</v>
+        <v>504692</v>
       </c>
       <c r="R35" t="n">
-        <v>7134666</v>
+        <v>7134770</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4581,6 +4581,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4607,10 +4612,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119929139</v>
+        <v>119929852</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4623,21 +4628,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4647,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504645</v>
+        <v>504662</v>
       </c>
       <c r="R36" t="n">
-        <v>7134818</v>
+        <v>7134848</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4709,10 +4714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119931675</v>
+        <v>119930718</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4725,21 +4730,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4749,13 +4754,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504635</v>
+        <v>504758</v>
       </c>
       <c r="R37" t="n">
-        <v>7134639</v>
+        <v>7134653</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4785,11 +4790,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4816,10 +4816,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119930231</v>
+        <v>119927666</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4832,21 +4832,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504728</v>
+        <v>504727</v>
       </c>
       <c r="R38" t="n">
-        <v>7134788</v>
+        <v>7134707</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4892,11 +4892,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4923,10 +4918,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119927331</v>
+        <v>119929519</v>
       </c>
       <c r="B39" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4935,25 +4930,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4963,13 +4958,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504635</v>
       </c>
       <c r="R39" t="n">
-        <v>7134684</v>
+        <v>7134835</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4999,6 +4994,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5025,10 +5025,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119930947</v>
+        <v>119931003</v>
       </c>
       <c r="B40" t="n">
-        <v>79658</v>
+        <v>78279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5037,25 +5037,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504733</v>
+        <v>504719</v>
       </c>
       <c r="R40" t="n">
-        <v>7134672</v>
+        <v>7134660</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119927769</v>
+        <v>119926813</v>
       </c>
       <c r="B41" t="n">
-        <v>90506</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504699</v>
+        <v>504786</v>
       </c>
       <c r="R41" t="n">
-        <v>7134737</v>
+        <v>7134692</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5197,12 +5197,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5229,7 +5234,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119930775</v>
+        <v>119928953</v>
       </c>
       <c r="B42" t="n">
         <v>78542</v>
@@ -5269,10 +5274,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504774</v>
+        <v>504662</v>
       </c>
       <c r="R42" t="n">
-        <v>7134657</v>
+        <v>7134813</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5336,10 +5341,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119927746</v>
+        <v>119927975</v>
       </c>
       <c r="B43" t="n">
-        <v>78187</v>
+        <v>90545</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5348,25 +5353,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5376,10 +5381,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504709</v>
+        <v>504681</v>
       </c>
       <c r="R43" t="n">
-        <v>7134715</v>
+        <v>7134773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5438,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119931003</v>
+        <v>119929139</v>
       </c>
       <c r="B44" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5454,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504719</v>
+        <v>504645</v>
       </c>
       <c r="R44" t="n">
-        <v>7134660</v>
+        <v>7134818</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5540,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119927937</v>
+        <v>119927769</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>90506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5556,21 +5561,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5580,10 +5585,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504692</v>
+        <v>504699</v>
       </c>
       <c r="R45" t="n">
-        <v>7134770</v>
+        <v>7134737</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5616,11 +5621,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,10 +5647,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119927666</v>
+        <v>119927959</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>90591</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5659,25 +5659,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504727</v>
+        <v>504676</v>
       </c>
       <c r="R46" t="n">
-        <v>7134707</v>
+        <v>7134783</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119930639</v>
+        <v>119930511</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5761,25 +5761,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
         <v>504746</v>
       </c>
       <c r="R47" t="n">
-        <v>7134714</v>
+        <v>7134757</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5825,11 +5825,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5856,10 +5851,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119930511</v>
+        <v>119927365</v>
       </c>
       <c r="B48" t="n">
-        <v>79652</v>
+        <v>92048</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5868,25 +5863,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5896,13 +5891,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504746</v>
+        <v>504727</v>
       </c>
       <c r="R48" t="n">
-        <v>7134757</v>
+        <v>7134690</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119926813</v>
+        <v>119927785</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5998,13 +5993,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504786</v>
+        <v>504704</v>
       </c>
       <c r="R49" t="n">
-        <v>7134692</v>
+        <v>7134755</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6028,17 +6023,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6065,10 +6055,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119931297</v>
+        <v>119931675</v>
       </c>
       <c r="B50" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6081,39 +6071,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504699</v>
+        <v>504635</v>
       </c>
       <c r="R50" t="n">
-        <v>7134659</v>
+        <v>7134639</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6146,6 +6131,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6172,10 +6162,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119929965</v>
+        <v>119932667</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6184,41 +6174,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504693</v>
+        <v>504661</v>
       </c>
       <c r="R51" t="n">
-        <v>7134811</v>
+        <v>7134863</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6274,10 +6273,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119930718</v>
+        <v>119931788</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
+        <v>90730</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6286,25 +6285,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6314,10 +6313,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504758</v>
+        <v>504645</v>
       </c>
       <c r="R52" t="n">
-        <v>7134653</v>
+        <v>7134625</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6376,10 +6375,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119931261</v>
+        <v>119931297</v>
       </c>
       <c r="B53" t="n">
-        <v>90825</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6388,41 +6387,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504693</v>
+        <v>504699</v>
       </c>
       <c r="R53" t="n">
-        <v>7134662</v>
+        <v>7134659</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6478,10 +6482,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119927326</v>
+        <v>119931261</v>
       </c>
       <c r="B54" t="n">
-        <v>79624</v>
+        <v>90825</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6490,25 +6494,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6518,10 +6522,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504726</v>
+        <v>504693</v>
       </c>
       <c r="R54" t="n">
-        <v>7134683</v>
+        <v>7134662</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6580,10 +6584,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119931788</v>
+        <v>119927179</v>
       </c>
       <c r="B55" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6592,25 +6596,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6620,10 +6624,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504645</v>
+        <v>504745</v>
       </c>
       <c r="R55" t="n">
-        <v>7134625</v>
+        <v>7134686</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6682,10 +6686,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119930524</v>
+        <v>119931444</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6698,21 +6702,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6722,13 +6726,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504748</v>
+        <v>504676</v>
       </c>
       <c r="R56" t="n">
-        <v>7134754</v>
+        <v>7134658</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6758,6 +6762,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6784,10 +6793,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119927276</v>
+        <v>119929031</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6796,25 +6805,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6824,13 +6833,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504730</v>
+        <v>504655</v>
       </c>
       <c r="R57" t="n">
-        <v>7134689</v>
+        <v>7134811</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6860,11 +6869,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6891,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119931555</v>
+        <v>119931600</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6903,25 +6907,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6931,13 +6935,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504644</v>
+        <v>504646</v>
       </c>
       <c r="R58" t="n">
-        <v>7134658</v>
+        <v>7134666</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6967,11 +6971,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7105,7 +7104,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119927785</v>
+        <v>119930775</v>
       </c>
       <c r="B60" t="n">
         <v>78542</v>
@@ -7145,10 +7144,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504704</v>
+        <v>504774</v>
       </c>
       <c r="R60" t="n">
-        <v>7134755</v>
+        <v>7134657</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7181,6 +7180,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7207,10 +7211,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119932667</v>
+        <v>119927276</v>
       </c>
       <c r="B61" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7219,47 +7223,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504661</v>
+        <v>504730</v>
       </c>
       <c r="R61" t="n">
-        <v>7134863</v>
+        <v>7134689</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7292,6 +7287,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927365</v>
+        <v>119927746</v>
       </c>
       <c r="B62" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504727</v>
+        <v>504709</v>
       </c>
       <c r="R62" t="n">
-        <v>7134690</v>
+        <v>7134715</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119931444</v>
+        <v>119929026</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7436,21 +7436,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504676</v>
+        <v>504650</v>
       </c>
       <c r="R63" t="n">
-        <v>7134658</v>
+        <v>7134810</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7496,11 +7496,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7527,10 +7522,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119929026</v>
+        <v>119929965</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7543,21 +7538,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7567,10 +7562,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504650</v>
+        <v>504693</v>
       </c>
       <c r="R64" t="n">
-        <v>7134810</v>
+        <v>7134811</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7629,10 +7624,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119927179</v>
+        <v>119928356</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7641,25 +7636,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7669,13 +7664,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504745</v>
+        <v>504674</v>
       </c>
       <c r="R65" t="n">
-        <v>7134686</v>
+        <v>7134819</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7705,6 +7700,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119928356</v>
+        <v>119930524</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7747,21 +7747,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504674</v>
+        <v>504748</v>
       </c>
       <c r="R66" t="n">
-        <v>7134819</v>
+        <v>7134754</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7807,11 +7807,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7838,10 +7833,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119929993</v>
+        <v>119927331</v>
       </c>
       <c r="B67" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7850,25 +7845,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7878,10 +7873,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504701</v>
+        <v>504726</v>
       </c>
       <c r="R67" t="n">
-        <v>7134814</v>
+        <v>7134684</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7940,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119929476</v>
+        <v>119930947</v>
       </c>
       <c r="B68" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7952,25 +7947,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7980,13 +7975,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504634</v>
+        <v>504733</v>
       </c>
       <c r="R68" t="n">
-        <v>7134847</v>
+        <v>7134672</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8042,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119927975</v>
+        <v>119930231</v>
       </c>
       <c r="B69" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8054,25 +8049,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8082,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504681</v>
+        <v>504728</v>
       </c>
       <c r="R69" t="n">
-        <v>7134773</v>
+        <v>7134788</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8118,6 +8113,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8144,7 +8144,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119930827</v>
+        <v>119929993</v>
       </c>
       <c r="B70" t="n">
         <v>78278</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504752</v>
+        <v>504701</v>
       </c>
       <c r="R70" t="n">
-        <v>7134670</v>
+        <v>7134814</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119927959</v>
+        <v>119929476</v>
       </c>
       <c r="B71" t="n">
-        <v>90591</v>
+        <v>78278</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8258,25 +8258,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504676</v>
+        <v>504634</v>
       </c>
       <c r="R71" t="n">
-        <v>7134783</v>
+        <v>7134847</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119929519</v>
+        <v>119930639</v>
       </c>
       <c r="B73" t="n">
         <v>78542</v>
@@ -8490,13 +8490,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504635</v>
+        <v>504746</v>
       </c>
       <c r="R73" t="n">
-        <v>7134835</v>
+        <v>7134714</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119928953</v>
+        <v>119931555</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8597,13 +8597,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504662</v>
+        <v>504644</v>
       </c>
       <c r="R74" t="n">
-        <v>7134813</v>
+        <v>7134658</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119929031</v>
+        <v>119927326</v>
       </c>
       <c r="B75" t="n">
-        <v>79583</v>
+        <v>79624</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8676,25 +8676,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504655</v>
+        <v>504726</v>
       </c>
       <c r="R75" t="n">
-        <v>7134811</v>
+        <v>7134683</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119966716</v>
+        <v>119966717</v>
       </c>
       <c r="B76" t="n">
         <v>78542</v>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>504767</v>
+        <v>504773</v>
       </c>
       <c r="R76" t="n">
-        <v>7134698</v>
+        <v>7134719</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119966717</v>
+        <v>119966716</v>
       </c>
       <c r="B77" t="n">
         <v>78542</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>504773</v>
+        <v>504767</v>
       </c>
       <c r="R77" t="n">
-        <v>7134719</v>
+        <v>7134698</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056729</v>
+        <v>120056742</v>
       </c>
       <c r="B78" t="n">
-        <v>79624</v>
+        <v>79527</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504742</v>
+        <v>504768</v>
       </c>
       <c r="R78" t="n">
-        <v>7134636</v>
+        <v>7134630</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På sälglåga.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9091,10 +9091,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056722</v>
+        <v>120056731</v>
       </c>
       <c r="B79" t="n">
-        <v>87423</v>
+        <v>79652</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9103,25 +9103,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504718</v>
+        <v>504742</v>
       </c>
       <c r="R79" t="n">
-        <v>7134606</v>
+        <v>7134636</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9170,6 +9170,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9409,10 +9414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056742</v>
+        <v>120056722</v>
       </c>
       <c r="B82" t="n">
-        <v>79527</v>
+        <v>87423</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9421,25 +9426,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6456</v>
+        <v>4412</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9452,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504768</v>
+        <v>504718</v>
       </c>
       <c r="R82" t="n">
-        <v>7134630</v>
+        <v>7134606</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9488,11 +9493,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9520,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056731</v>
+        <v>120056729</v>
       </c>
       <c r="B83" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9532,25 +9532,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119927812</v>
+        <v>119929852</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504703</v>
+        <v>504662</v>
       </c>
       <c r="R33" t="n">
-        <v>7134764</v>
+        <v>7134848</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4403,10 +4403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119930827</v>
+        <v>119930231</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504752</v>
+        <v>504728</v>
       </c>
       <c r="R34" t="n">
-        <v>7134670</v>
+        <v>7134788</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4479,6 +4479,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4505,10 +4510,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119927937</v>
+        <v>119930827</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4521,21 +4526,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4545,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504692</v>
+        <v>504752</v>
       </c>
       <c r="R35" t="n">
-        <v>7134770</v>
+        <v>7134670</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4581,11 +4586,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4612,10 +4612,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119929852</v>
+        <v>119930947</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>79658</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4624,25 +4624,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504662</v>
+        <v>504733</v>
       </c>
       <c r="R36" t="n">
-        <v>7134848</v>
+        <v>7134672</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119927666</v>
+        <v>119931261</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>90825</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4828,25 +4828,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504727</v>
+        <v>504693</v>
       </c>
       <c r="R38" t="n">
-        <v>7134707</v>
+        <v>7134662</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119929519</v>
+        <v>119932667</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4930,38 +4930,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504635</v>
+        <v>504661</v>
       </c>
       <c r="R39" t="n">
-        <v>7134835</v>
+        <v>7134863</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4994,11 +5003,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5025,10 +5029,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119931003</v>
+        <v>119929965</v>
       </c>
       <c r="B40" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5041,21 +5045,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5065,10 +5069,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504719</v>
+        <v>504693</v>
       </c>
       <c r="R40" t="n">
-        <v>7134660</v>
+        <v>7134811</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,7 +5131,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119926813</v>
+        <v>119931555</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -5167,10 +5171,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504786</v>
+        <v>504644</v>
       </c>
       <c r="R41" t="n">
-        <v>7134692</v>
+        <v>7134658</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5197,12 +5201,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5234,7 +5238,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119928953</v>
+        <v>119931444</v>
       </c>
       <c r="B42" t="n">
         <v>78542</v>
@@ -5274,13 +5278,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504662</v>
+        <v>504676</v>
       </c>
       <c r="R42" t="n">
-        <v>7134813</v>
+        <v>7134658</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5341,10 +5345,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119927975</v>
+        <v>119927937</v>
       </c>
       <c r="B43" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,25 +5357,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5381,13 +5385,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504681</v>
+        <v>504692</v>
       </c>
       <c r="R43" t="n">
-        <v>7134773</v>
+        <v>7134770</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5417,6 +5421,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5443,10 +5452,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119929139</v>
+        <v>119931788</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>90730</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5455,25 +5464,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5486,7 +5495,7 @@
         <v>504645</v>
       </c>
       <c r="R44" t="n">
-        <v>7134818</v>
+        <v>7134625</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5545,10 +5554,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119927769</v>
+        <v>119928953</v>
       </c>
       <c r="B45" t="n">
-        <v>90506</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5561,21 +5570,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,10 +5594,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504699</v>
+        <v>504662</v>
       </c>
       <c r="R45" t="n">
-        <v>7134737</v>
+        <v>7134813</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5621,6 +5630,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,10 +5661,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119927959</v>
+        <v>119927276</v>
       </c>
       <c r="B46" t="n">
-        <v>90591</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5659,25 +5673,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5687,13 +5701,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504676</v>
+        <v>504730</v>
       </c>
       <c r="R46" t="n">
-        <v>7134783</v>
+        <v>7134689</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5723,6 +5737,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5749,10 +5768,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119930511</v>
+        <v>119927666</v>
       </c>
       <c r="B47" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5761,25 +5780,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5789,10 +5808,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504746</v>
+        <v>504727</v>
       </c>
       <c r="R47" t="n">
-        <v>7134757</v>
+        <v>7134707</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5851,10 +5870,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119927365</v>
+        <v>119927812</v>
       </c>
       <c r="B48" t="n">
-        <v>92048</v>
+        <v>90580</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5867,21 +5886,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5891,13 +5910,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504727</v>
+        <v>504703</v>
       </c>
       <c r="R48" t="n">
-        <v>7134690</v>
+        <v>7134764</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5953,10 +5972,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119927785</v>
+        <v>119930524</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5969,21 +5988,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5993,13 +6012,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504704</v>
+        <v>504748</v>
       </c>
       <c r="R49" t="n">
-        <v>7134755</v>
+        <v>7134754</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6055,7 +6074,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119931675</v>
+        <v>119930639</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -6095,13 +6114,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504635</v>
+        <v>504746</v>
       </c>
       <c r="R50" t="n">
-        <v>7134639</v>
+        <v>7134714</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6162,10 +6181,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119932667</v>
+        <v>119927326</v>
       </c>
       <c r="B51" t="n">
-        <v>56532</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6174,50 +6193,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504661</v>
+        <v>504726</v>
       </c>
       <c r="R51" t="n">
-        <v>7134863</v>
+        <v>7134683</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6273,10 +6283,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119931788</v>
+        <v>119929476</v>
       </c>
       <c r="B52" t="n">
-        <v>90730</v>
+        <v>78278</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6285,25 +6295,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6313,13 +6323,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504645</v>
+        <v>504634</v>
       </c>
       <c r="R52" t="n">
-        <v>7134625</v>
+        <v>7134847</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6375,10 +6385,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119931297</v>
+        <v>119929031</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>79583</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6387,46 +6397,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504699</v>
+        <v>504655</v>
       </c>
       <c r="R53" t="n">
-        <v>7134659</v>
+        <v>7134811</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6482,10 +6487,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119931261</v>
+        <v>119926813</v>
       </c>
       <c r="B54" t="n">
-        <v>90825</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6494,25 +6499,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6522,13 +6527,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504693</v>
+        <v>504786</v>
       </c>
       <c r="R54" t="n">
-        <v>7134662</v>
+        <v>7134692</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6552,12 +6557,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6584,10 +6594,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119927179</v>
+        <v>119927331</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6600,21 +6610,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6624,10 +6634,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504745</v>
+        <v>504726</v>
       </c>
       <c r="R55" t="n">
-        <v>7134686</v>
+        <v>7134684</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6686,10 +6696,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119931444</v>
+        <v>119930503</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6702,21 +6712,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6726,13 +6736,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504676</v>
+        <v>504740</v>
       </c>
       <c r="R56" t="n">
-        <v>7134658</v>
+        <v>7134766</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6762,11 +6772,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6793,10 +6798,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119929031</v>
+        <v>119927179</v>
       </c>
       <c r="B57" t="n">
-        <v>79583</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6809,21 +6814,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6833,10 +6838,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504655</v>
+        <v>504745</v>
       </c>
       <c r="R57" t="n">
-        <v>7134811</v>
+        <v>7134686</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6895,10 +6900,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119931600</v>
+        <v>119927975</v>
       </c>
       <c r="B58" t="n">
-        <v>79659</v>
+        <v>90545</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6911,21 +6916,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6935,10 +6940,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504646</v>
+        <v>504681</v>
       </c>
       <c r="R58" t="n">
-        <v>7134666</v>
+        <v>7134773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6997,7 +7002,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119930581</v>
+        <v>119929519</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -7037,13 +7042,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504741</v>
+        <v>504635</v>
       </c>
       <c r="R59" t="n">
-        <v>7134737</v>
+        <v>7134835</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7211,10 +7216,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119927276</v>
+        <v>119931003</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7227,21 +7232,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7251,13 +7256,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504730</v>
+        <v>504719</v>
       </c>
       <c r="R61" t="n">
-        <v>7134689</v>
+        <v>7134660</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7287,11 +7292,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927746</v>
+        <v>119929026</v>
       </c>
       <c r="B62" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7358,13 +7358,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504709</v>
+        <v>504650</v>
       </c>
       <c r="R62" t="n">
-        <v>7134715</v>
+        <v>7134810</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119929026</v>
+        <v>119927746</v>
       </c>
       <c r="B63" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7436,21 +7436,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504650</v>
+        <v>504709</v>
       </c>
       <c r="R63" t="n">
-        <v>7134810</v>
+        <v>7134715</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7522,10 +7522,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119929965</v>
+        <v>119927365</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7538,21 +7538,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504693</v>
+        <v>504727</v>
       </c>
       <c r="R64" t="n">
-        <v>7134811</v>
+        <v>7134690</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119928356</v>
+        <v>119927785</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7664,13 +7664,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504674</v>
+        <v>504704</v>
       </c>
       <c r="R65" t="n">
-        <v>7134819</v>
+        <v>7134755</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7700,11 +7700,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7731,10 +7726,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119930524</v>
+        <v>119928356</v>
       </c>
       <c r="B66" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7747,21 +7742,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7771,13 +7766,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504748</v>
+        <v>504674</v>
       </c>
       <c r="R66" t="n">
-        <v>7134754</v>
+        <v>7134819</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7807,6 +7802,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7833,10 +7833,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119927331</v>
+        <v>119929993</v>
       </c>
       <c r="B67" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7845,25 +7845,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7873,10 +7873,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504726</v>
+        <v>504701</v>
       </c>
       <c r="R67" t="n">
-        <v>7134684</v>
+        <v>7134814</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119930947</v>
+        <v>119927769</v>
       </c>
       <c r="B68" t="n">
-        <v>79658</v>
+        <v>90506</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7947,25 +7947,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>3242</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504733</v>
+        <v>504699</v>
       </c>
       <c r="R68" t="n">
-        <v>7134672</v>
+        <v>7134737</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119930231</v>
+        <v>119929139</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8053,21 +8053,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504728</v>
+        <v>504645</v>
       </c>
       <c r="R69" t="n">
-        <v>7134788</v>
+        <v>7134818</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8113,11 +8113,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8144,10 +8139,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119929993</v>
+        <v>119930581</v>
       </c>
       <c r="B70" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,21 +8155,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8179,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504701</v>
+        <v>504741</v>
       </c>
       <c r="R70" t="n">
-        <v>7134814</v>
+        <v>7134737</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8220,6 +8215,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8246,10 +8246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119929476</v>
+        <v>119931675</v>
       </c>
       <c r="B71" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504634</v>
+        <v>504635</v>
       </c>
       <c r="R71" t="n">
-        <v>7134847</v>
+        <v>7134639</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8322,6 +8322,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8348,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119930503</v>
+        <v>119930511</v>
       </c>
       <c r="B72" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8360,25 +8365,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8388,10 +8393,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504740</v>
+        <v>504746</v>
       </c>
       <c r="R72" t="n">
-        <v>7134766</v>
+        <v>7134757</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8450,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119930639</v>
+        <v>119931297</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8466,37 +8471,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504746</v>
+        <v>504699</v>
       </c>
       <c r="R73" t="n">
-        <v>7134714</v>
+        <v>7134659</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8526,11 +8536,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8557,10 +8562,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119931555</v>
+        <v>119927959</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>90591</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8569,25 +8574,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8597,13 +8602,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>504644</v>
+        <v>504676</v>
       </c>
       <c r="R74" t="n">
-        <v>7134658</v>
+        <v>7134783</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8633,11 +8638,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8664,10 +8664,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119927326</v>
+        <v>119931600</v>
       </c>
       <c r="B75" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8676,25 +8676,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8704,13 +8704,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>504726</v>
+        <v>504646</v>
       </c>
       <c r="R75" t="n">
-        <v>7134683</v>
+        <v>7134666</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120056742</v>
+        <v>120056729</v>
       </c>
       <c r="B78" t="n">
-        <v>79527</v>
+        <v>79624</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>504768</v>
+        <v>504742</v>
       </c>
       <c r="R78" t="n">
-        <v>7134630</v>
+        <v>7134636</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9091,10 +9091,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120056731</v>
+        <v>120056742</v>
       </c>
       <c r="B79" t="n">
-        <v>79652</v>
+        <v>79527</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9107,21 +9107,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>504742</v>
+        <v>504768</v>
       </c>
       <c r="R79" t="n">
-        <v>7134636</v>
+        <v>7134630</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På sälglåga.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9308,10 +9308,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120056747</v>
+        <v>120056722</v>
       </c>
       <c r="B81" t="n">
-        <v>91858</v>
+        <v>87423</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9320,25 +9320,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>504755</v>
+        <v>504718</v>
       </c>
       <c r="R81" t="n">
-        <v>7134686</v>
+        <v>7134606</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120056722</v>
+        <v>120056731</v>
       </c>
       <c r="B82" t="n">
-        <v>87423</v>
+        <v>79652</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9426,25 +9426,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>504718</v>
+        <v>504742</v>
       </c>
       <c r="R82" t="n">
-        <v>7134606</v>
+        <v>7134636</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9493,6 +9493,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9520,10 +9525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120056729</v>
+        <v>120056747</v>
       </c>
       <c r="B83" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9532,25 +9537,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9563,10 +9568,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>504742</v>
+        <v>504755</v>
       </c>
       <c r="R83" t="n">
-        <v>7134636</v>
+        <v>7134686</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9599,11 +9604,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På sälglåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -8458,7 +8458,7 @@
         <v>119931297</v>
       </c>
       <c r="B73" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -8473,11 +8473,6 @@
       <c r="E73" t="n">
         <v>103021</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -8458,7 +8458,7 @@
         <v>119931297</v>
       </c>
       <c r="B73" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8472,6 +8472,11 @@
       </c>
       <c r="E73" t="n">
         <v>103021</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>

--- a/artfynd/A 26044-2024 artfynd.xlsx
+++ b/artfynd/A 26044-2024 artfynd.xlsx
@@ -8458,7 +8458,7 @@
         <v>119931297</v>
       </c>
       <c r="B73" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
